--- a/songs/mayday/data/mayday_songs.xlsx
+++ b/songs/mayday/data/mayday_songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1/Code/net_charts/songs/mayday/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF9E425-D4E9-9845-94B7-CF5531EDCB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225F6BEF-F0E0-CF42-82F2-BEFC019E9E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21560" yWindow="4160" windowWidth="28100" windowHeight="17360" xr2:uid="{83F95A99-0641-214A-BFE5-EC231FCA42BA}"/>
+    <workbookView xWindow="8380" yWindow="600" windowWidth="28100" windowHeight="17360" xr2:uid="{83F95A99-0641-214A-BFE5-EC231FCA42BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="38" r:id="rId3"/>
+    <pivotCache cacheId="52" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="180">
   <si>
     <t>album_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -508,19 +508,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>行标签</t>
-  </si>
-  <si>
     <t>总计</t>
-  </si>
-  <si>
-    <t>计数项:song_name</t>
-  </si>
-  <si>
-    <t>求和项:is_duplicate</t>
-  </si>
-  <si>
-    <t>求和项:has_lyric</t>
   </si>
   <si>
     <t>album_type</t>
@@ -566,6 +554,51 @@
   </si>
   <si>
     <t>步步 自选作品辑</t>
+  </si>
+  <si>
+    <t>album_name</t>
+  </si>
+  <si>
+    <t>song_name</t>
+  </si>
+  <si>
+    <t>爱情万岁 汇总</t>
+  </si>
+  <si>
+    <t>步步 自选作品辑 汇总</t>
+  </si>
+  <si>
+    <t>第二人生 (明日版) 汇总</t>
+  </si>
+  <si>
+    <t>第二人生 (末日版) 汇总</t>
+  </si>
+  <si>
+    <t>第一张创作专辑 汇总</t>
+  </si>
+  <si>
+    <t>后青春期的诗 汇总</t>
+  </si>
+  <si>
+    <t>人生海海 汇总</t>
+  </si>
+  <si>
+    <t>神的孩子都在跳舞 汇总</t>
+  </si>
+  <si>
+    <t>时光机 汇总</t>
+  </si>
+  <si>
+    <t>为爱而生 汇总</t>
+  </si>
+  <si>
+    <t>知足 最真杰作选 汇总</t>
+  </si>
+  <si>
+    <t>自传 汇总</t>
+  </si>
+  <si>
+    <t>计数项:album_name</t>
   </si>
 </sst>
 </file>
@@ -641,8 +674,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,22 +695,38 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="m1" refreshedDate="46047.750113078706" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="160" xr:uid="{C48C2AD5-406D-9641-953A-A989CD98CCD7}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="m1" refreshedDate="46047.80786724537" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="190" xr:uid="{1B8A15CB-7EFB-864D-BBFD-435B64949287}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:K161" sheet="Sheet1"/>
+    <worksheetSource ref="A1:K191" sheet="Sheet1"/>
   </cacheSource>
-  <cacheFields count="13">
+  <cacheFields count="14">
     <cacheField name="album_order" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="11"/>
     </cacheField>
     <cacheField name="album_id" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="38214" maxValue="34746073"/>
     </cacheField>
     <cacheField name="album_name" numFmtId="0">
+      <sharedItems count="12">
+        <s v="第一张创作专辑"/>
+        <s v="爱情万岁"/>
+        <s v="人生海海"/>
+        <s v="时光机"/>
+        <s v="神的孩子都在跳舞"/>
+        <s v="为爱而生"/>
+        <s v="后青春期的诗"/>
+        <s v="第二人生 (明日版)"/>
+        <s v="第二人生 (末日版)"/>
+        <s v="自传"/>
+        <s v="知足 最真杰作选"/>
+        <s v="步步 自选作品辑"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="album_type" numFmtId="0">
       <sharedItems/>
     </cacheField>
     <cacheField name="release_date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1999-07-07T00:00:00" maxDate="2016-07-22T00:00:00" count="10">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1999-07-07T00:00:00" maxDate="2016-07-22T00:00:00" count="40">
         <d v="1999-07-07T00:00:00"/>
         <d v="2000-07-07T00:00:00"/>
         <d v="2001-07-06T00:00:00"/>
@@ -688,8 +737,38 @@
         <d v="2011-12-16T00:00:00"/>
         <d v="2016-07-21T00:00:00"/>
         <d v="2005-08-26T00:00:00"/>
+        <d v="2013-12-30T00:00:00"/>
+        <d v="2013-12-31T00:00:00"/>
+        <d v="2014-01-01T00:00:00"/>
+        <d v="2014-01-02T00:00:00"/>
+        <d v="2014-01-03T00:00:00"/>
+        <d v="2014-01-04T00:00:00"/>
+        <d v="2014-01-05T00:00:00"/>
+        <d v="2014-01-06T00:00:00"/>
+        <d v="2014-01-07T00:00:00"/>
+        <d v="2014-01-08T00:00:00"/>
+        <d v="2014-01-09T00:00:00"/>
+        <d v="2014-01-10T00:00:00"/>
+        <d v="2014-01-11T00:00:00"/>
+        <d v="2014-01-12T00:00:00"/>
+        <d v="2014-01-13T00:00:00"/>
+        <d v="2014-01-14T00:00:00"/>
+        <d v="2014-01-15T00:00:00"/>
+        <d v="2014-01-16T00:00:00"/>
+        <d v="2014-01-17T00:00:00"/>
+        <d v="2014-01-18T00:00:00"/>
+        <d v="2014-01-19T00:00:00"/>
+        <d v="2014-01-20T00:00:00"/>
+        <d v="2014-01-21T00:00:00"/>
+        <d v="2014-01-22T00:00:00"/>
+        <d v="2014-01-23T00:00:00"/>
+        <d v="2014-01-24T00:00:00"/>
+        <d v="2014-01-25T00:00:00"/>
+        <d v="2014-01-26T00:00:00"/>
+        <d v="2014-01-27T00:00:00"/>
+        <d v="2014-01-28T00:00:00"/>
       </sharedItems>
-      <fieldGroup par="12"/>
+      <fieldGroup par="13"/>
     </cacheField>
     <cacheField name="song_order" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="30"/>
@@ -698,10 +777,151 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="385542" maxValue="2008204010"/>
     </cacheField>
     <cacheField name="song_name" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2012" maxValue="2012"/>
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2012" maxValue="2012" count="140">
+        <s v="疯狂世界"/>
+        <s v="拥抱"/>
+        <s v="透露"/>
+        <s v="生活"/>
+        <s v="爱情的模样"/>
+        <s v="嘿！我要走了"/>
+        <s v="轧车"/>
+        <s v="志明与春娇"/>
+        <s v="HoSee"/>
+        <s v="黑白讲"/>
+        <s v="I Love You 无望"/>
+        <s v="风若吹"/>
+        <s v="为什么 (今日的爱情)"/>
+        <s v="终结孤单"/>
+        <s v="明白"/>
+        <s v="心中无别人"/>
+        <s v="有你的将来"/>
+        <s v="憨人"/>
+        <s v="叫我第一名"/>
+        <s v="雨眠"/>
+        <s v="罗密欧与茱丽叶"/>
+        <s v="温柔"/>
+        <s v="爱情万岁"/>
+        <s v="反而"/>
+        <s v="一颗苹果"/>
+        <s v="能不能不要说"/>
+        <s v="好不好"/>
+        <s v="相信"/>
+        <s v="Ok啦"/>
+        <s v="借问众神明"/>
+        <s v="永远的永远"/>
+        <s v="彩虹"/>
+        <s v="啾啾啾"/>
+        <s v="纯真"/>
+        <s v="候鸟"/>
+        <s v="人生海海"/>
+        <s v="轻功"/>
+        <s v="恒星的恒心"/>
+        <s v="雌雄同体"/>
+        <s v="阿姆斯壮"/>
+        <s v="而我知道"/>
+        <s v="赌神"/>
+        <s v="别惹我"/>
+        <s v="九号球"/>
+        <s v="武装"/>
+        <s v="时光机"/>
+        <s v="我们 (时时刻刻)"/>
+        <s v="在这一秒"/>
+        <s v="生命有一种绝对"/>
+        <s v="王子面"/>
+        <s v="小时候"/>
+        <s v="孙悟空"/>
+        <s v="倔强"/>
+        <s v="垃圾车"/>
+        <s v="小护士"/>
+        <s v="让我照顾你"/>
+        <s v="约翰蓝侬"/>
+        <s v="回来吧"/>
+        <s v="错错错"/>
+        <s v="晚安，地球人"/>
+        <s v="超人"/>
+        <s v="神的孩子都在跳舞"/>
+        <s v="圣诞夜惊魂"/>
+        <s v="垃圾车(朋友版)"/>
+        <s v="前传"/>
+        <s v="为爱而生"/>
+        <s v="天使"/>
+        <s v="我又初恋了"/>
+        <s v="香水"/>
+        <s v="摩托车日记"/>
+        <s v="最重要的小事"/>
+        <s v="快乐很伟大"/>
+        <s v="忘词"/>
+        <s v="宠上天"/>
+        <s v="米老鼠"/>
+        <s v="一千个世纪"/>
+        <s v="胎音"/>
+        <s v="突然好想你"/>
+        <s v="生存以上 生活以下"/>
+        <s v="你不是真正的快乐"/>
+        <s v="爆肝"/>
+        <s v="噢买尬"/>
+        <s v="出头天"/>
+        <s v="我心中尚未崩坏的地方"/>
+        <s v="春天的呐喊"/>
+        <s v="夜访吸血鬼"/>
+        <s v="如烟"/>
+        <s v="后青春期的诗"/>
+        <s v="笑忘歌"/>
+        <s v="有些事现在不做 一辈子都不会做了"/>
+        <s v="我不愿让你一个人"/>
+        <s v="星空"/>
+        <s v="洗衣机"/>
+        <s v="三个傻瓜"/>
+        <s v="歪腰"/>
+        <s v="干杯"/>
+        <s v="仓颉"/>
+        <n v="2012"/>
+        <s v="第二人生"/>
+        <s v="诺亚方舟"/>
+        <s v="明日"/>
+        <s v="OAOA (现在就是永远)"/>
+        <s v="T1213121"/>
+        <s v="末日"/>
+        <s v="OAOA (丢掉名字性别)"/>
+        <s v="如果我们不曾相遇"/>
+        <s v="成名在望"/>
+        <s v="好好 (想把你写成一首歌)"/>
+        <s v="兄弟"/>
+        <s v="人生有限公司"/>
+        <s v="后来的我们"/>
+        <s v="顽固"/>
+        <s v="派对动物"/>
+        <s v="最好的一天"/>
+        <s v="少年他的奇幻漂流"/>
+        <s v="终于结束的起点"/>
+        <s v="任意门"/>
+        <s v="转眼"/>
+        <s v="知足"/>
+        <s v="牙关"/>
+        <s v="乱世浮生"/>
+        <s v="恋爱ing"/>
+        <s v="听不到"/>
+        <s v="温柔 (还你自由版)"/>
+        <s v="金多虾"/>
+        <s v="麦来乱"/>
+        <s v="OK 啦"/>
+        <s v="垃圾车 (朋友版)"/>
+        <s v="未来 (Sailing With Me)"/>
+        <s v="咸鱼"/>
+        <s v="步步"/>
+        <s v="拥抱 (2013新录制作品)"/>
+        <s v="伤心的人别听慢歌(贯彻快乐)"/>
+        <s v="洋葱 (2013新录制作品)"/>
+        <s v="入阵曲"/>
+        <s v="离开地球表面"/>
+        <s v="知足 (乐团版)"/>
+        <s v="温柔 (2013Remix版)"/>
+        <s v="你是唯一 (2013新录制作品)"/>
+        <s v="盛夏光年"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="album_fixed" numFmtId="0">
-      <sharedItems count="10">
+      <sharedItems count="11">
         <s v="第一张创作专辑"/>
         <s v="爱情万岁"/>
         <s v="人生海海"/>
@@ -712,6 +932,7 @@
         <s v="第二人生"/>
         <s v="自传"/>
         <s v="知足 最真杰作选"/>
+        <s v="步步 自选作品辑"/>
       </sharedItems>
     </cacheField>
     <cacheField name="has_lyric" numFmtId="0">
@@ -721,7 +942,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="月(release_date)" numFmtId="0" databaseField="0">
-      <fieldGroup base="3">
+      <fieldGroup base="4">
         <rangePr groupBy="months" startDate="1999-07-07T00:00:00" endDate="2016-07-22T00:00:00"/>
         <groupItems count="14">
           <s v="&lt;1999/7/7"/>
@@ -742,7 +963,7 @@
       </fieldGroup>
     </cacheField>
     <cacheField name="季度(release_date)" numFmtId="0" databaseField="0">
-      <fieldGroup base="3">
+      <fieldGroup base="4">
         <rangePr groupBy="quarters" startDate="1999-07-07T00:00:00" endDate="2016-07-22T00:00:00"/>
         <groupItems count="6">
           <s v="&lt;1999/7/7"/>
@@ -755,7 +976,7 @@
       </fieldGroup>
     </cacheField>
     <cacheField name="年(release_date)" numFmtId="0" databaseField="0">
-      <fieldGroup base="3">
+      <fieldGroup base="4">
         <rangePr groupBy="years" startDate="1999-07-07T00:00:00" endDate="2016-07-22T00:00:00"/>
         <groupItems count="20">
           <s v="&lt;1999/7/7"/>
@@ -791,27 +1012,29 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="160">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="190">
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
     <x v="0"/>
+    <s v="录音室专辑"/>
+    <x v="0"/>
     <n v="1"/>
     <n v="386925"/>
-    <s v="疯狂世界"/>
     <x v="0"/>
+    <x v="0"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="2"/>
     <n v="386927"/>
-    <s v="拥抱"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -819,11 +1042,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="3"/>
     <n v="386929"/>
-    <s v="透露"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -831,11 +1055,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="4"/>
     <n v="386930"/>
-    <s v="生活"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -843,11 +1068,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="5"/>
     <n v="386931"/>
-    <s v="爱情的模样"/>
+    <x v="4"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -855,11 +1081,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="6"/>
     <n v="386932"/>
-    <s v="嘿！我要走了"/>
+    <x v="5"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -867,11 +1094,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="7"/>
     <n v="386934"/>
-    <s v="轧车"/>
+    <x v="6"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -879,11 +1107,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="8"/>
     <n v="386936"/>
-    <s v="志明与春娇"/>
+    <x v="7"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -891,11 +1120,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="9"/>
     <n v="386939"/>
-    <s v="HoSee"/>
+    <x v="8"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -903,11 +1133,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="10"/>
     <n v="386942"/>
-    <s v="黑白讲"/>
+    <x v="9"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -915,11 +1146,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="11"/>
     <n v="386948"/>
-    <s v="I Love You 无望"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -927,11 +1159,12 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <s v="第一张创作专辑"/>
+    <x v="0"/>
+    <s v="录音室专辑"/>
     <x v="0"/>
     <n v="12"/>
     <n v="386951"/>
-    <s v="风若吹"/>
+    <x v="11"/>
     <x v="0"/>
     <n v="1"/>
     <n v="0"/>
@@ -939,11 +1172,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
     <x v="1"/>
+    <s v="录音室专辑"/>
+    <x v="1"/>
     <n v="1"/>
     <n v="386839"/>
-    <s v="为什么 (今日的爱情)"/>
+    <x v="12"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -951,11 +1185,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="2"/>
     <n v="386842"/>
-    <s v="终结孤单"/>
+    <x v="13"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -963,11 +1198,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="3"/>
     <n v="386846"/>
-    <s v="明白"/>
+    <x v="14"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -975,11 +1211,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="4"/>
     <n v="386848"/>
-    <s v="心中无别人"/>
+    <x v="15"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -987,11 +1224,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="5"/>
     <n v="386851"/>
-    <s v="有你的将来"/>
+    <x v="16"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -999,11 +1237,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="6"/>
     <n v="386854"/>
-    <s v="憨人"/>
+    <x v="17"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -1011,11 +1250,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="7"/>
     <n v="386857"/>
-    <s v="叫我第一名"/>
+    <x v="18"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -1023,11 +1263,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="8"/>
     <n v="386860"/>
-    <s v="雨眠"/>
+    <x v="19"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -1035,11 +1276,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="9"/>
     <n v="386863"/>
-    <s v="罗密欧与茱丽叶"/>
+    <x v="20"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -1047,11 +1289,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="10"/>
     <n v="386866"/>
-    <s v="温柔"/>
+    <x v="21"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -1059,11 +1302,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="11"/>
     <n v="386870"/>
-    <s v="爱情万岁"/>
+    <x v="22"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -1071,11 +1315,12 @@
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <s v="爱情万岁"/>
+    <x v="1"/>
+    <s v="录音室专辑"/>
     <x v="1"/>
     <n v="12"/>
     <n v="386874"/>
-    <s v="反而"/>
+    <x v="23"/>
     <x v="1"/>
     <n v="1"/>
     <n v="0"/>
@@ -1083,11 +1328,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
     <x v="2"/>
+    <s v="录音室专辑"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="386691"/>
-    <s v="一颗苹果"/>
+    <x v="24"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1095,11 +1341,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="2"/>
     <n v="386694"/>
-    <s v="能不能不要说"/>
+    <x v="25"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1107,11 +1354,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="3"/>
     <n v="386697"/>
-    <s v="好不好"/>
+    <x v="26"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1119,11 +1367,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="4"/>
     <n v="386700"/>
-    <s v="相信"/>
+    <x v="27"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1131,11 +1380,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="5"/>
     <n v="386702"/>
-    <s v="Ok啦"/>
+    <x v="28"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1143,11 +1393,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="6"/>
     <n v="386705"/>
-    <s v="借问众神明"/>
+    <x v="29"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1155,11 +1406,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="7"/>
     <n v="386709"/>
-    <s v="永远的永远"/>
+    <x v="30"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1167,11 +1419,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="8"/>
     <n v="386711"/>
-    <s v="彩虹"/>
+    <x v="31"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1179,11 +1432,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="9"/>
     <n v="386713"/>
-    <s v="啾啾啾"/>
+    <x v="32"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1191,11 +1445,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="10"/>
     <n v="386715"/>
-    <s v="纯真"/>
+    <x v="33"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1203,11 +1458,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="11"/>
     <n v="386716"/>
-    <s v="候鸟"/>
+    <x v="34"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1215,11 +1471,12 @@
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <s v="人生海海"/>
+    <x v="2"/>
+    <s v="录音室专辑"/>
     <x v="2"/>
     <n v="12"/>
     <n v="386717"/>
-    <s v="人生海海"/>
+    <x v="35"/>
     <x v="2"/>
     <n v="1"/>
     <n v="0"/>
@@ -1227,11 +1484,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
     <x v="3"/>
+    <s v="录音室专辑"/>
+    <x v="3"/>
     <n v="1"/>
     <n v="386443"/>
-    <s v="轻功"/>
+    <x v="36"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1239,11 +1497,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="2"/>
     <n v="386445"/>
-    <s v="恒星的恒心"/>
+    <x v="37"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1251,11 +1510,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="3"/>
     <n v="386447"/>
-    <s v="雌雄同体"/>
+    <x v="38"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1263,11 +1523,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="4"/>
     <n v="386449"/>
-    <s v="阿姆斯壮"/>
+    <x v="39"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1275,11 +1536,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="5"/>
     <n v="386451"/>
-    <s v="而我知道"/>
+    <x v="40"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1287,11 +1549,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="6"/>
     <n v="386453"/>
-    <s v="赌神"/>
+    <x v="41"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1299,11 +1562,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="7"/>
     <n v="386457"/>
-    <s v="别惹我"/>
+    <x v="42"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1311,11 +1575,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="8"/>
     <n v="386461"/>
-    <s v="九号球"/>
+    <x v="43"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1323,11 +1588,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="9"/>
     <n v="386465"/>
-    <s v="武装"/>
+    <x v="44"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1335,11 +1601,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="10"/>
     <n v="386469"/>
-    <s v="时光机"/>
+    <x v="45"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1347,11 +1614,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="11"/>
     <n v="386473"/>
-    <s v="我们 (时时刻刻)"/>
+    <x v="46"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1359,11 +1627,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="12"/>
     <n v="386476"/>
-    <s v="在这一秒"/>
+    <x v="47"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1371,11 +1640,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="13"/>
     <n v="386479"/>
-    <s v="生命有一种绝对"/>
+    <x v="48"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1383,11 +1653,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="14"/>
     <n v="386482"/>
-    <s v="王子面"/>
+    <x v="49"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1395,11 +1666,12 @@
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <s v="时光机"/>
+    <x v="3"/>
+    <s v="录音室专辑"/>
     <x v="3"/>
     <n v="15"/>
     <n v="386485"/>
-    <s v="小时候"/>
+    <x v="50"/>
     <x v="3"/>
     <n v="1"/>
     <n v="0"/>
@@ -1407,11 +1679,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
     <x v="4"/>
+    <s v="录音室专辑"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="386173"/>
-    <s v="孙悟空"/>
+    <x v="51"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1419,11 +1692,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="2"/>
     <n v="386175"/>
-    <s v="倔强"/>
+    <x v="52"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1431,11 +1705,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="3"/>
     <n v="386177"/>
-    <s v="垃圾车"/>
+    <x v="53"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1443,11 +1718,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="4"/>
     <n v="386179"/>
-    <s v="小护士"/>
+    <x v="54"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1455,11 +1731,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="5"/>
     <n v="386181"/>
-    <s v="让我照顾你"/>
+    <x v="55"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1467,11 +1744,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="6"/>
     <n v="386183"/>
-    <s v="约翰蓝侬"/>
+    <x v="56"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1479,11 +1757,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="7"/>
     <n v="386185"/>
-    <s v="回来吧"/>
+    <x v="57"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1491,11 +1770,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="8"/>
     <n v="386187"/>
-    <s v="错错错"/>
+    <x v="58"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1503,11 +1783,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="9"/>
     <n v="386189"/>
-    <s v="晚安，地球人"/>
+    <x v="59"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1515,11 +1796,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="10"/>
     <n v="386191"/>
-    <s v="超人"/>
+    <x v="60"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1527,11 +1809,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="11"/>
     <n v="386193"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="61"/>
     <x v="4"/>
     <n v="0"/>
     <n v="0"/>
@@ -1539,11 +1822,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="12"/>
     <n v="386195"/>
-    <s v="圣诞夜惊魂"/>
+    <x v="62"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1551,11 +1835,12 @@
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <s v="神的孩子都在跳舞"/>
+    <x v="4"/>
+    <s v="录音室专辑"/>
     <x v="4"/>
     <n v="13"/>
     <n v="386197"/>
-    <s v="垃圾车(朋友版)"/>
+    <x v="63"/>
     <x v="4"/>
     <n v="1"/>
     <n v="0"/>
@@ -1563,11 +1848,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
     <x v="5"/>
+    <s v="录音室专辑"/>
+    <x v="5"/>
     <n v="1"/>
     <n v="385884"/>
-    <s v="前传"/>
+    <x v="64"/>
     <x v="5"/>
     <n v="0"/>
     <n v="0"/>
@@ -1575,11 +1861,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="2"/>
     <n v="385887"/>
-    <s v="为爱而生"/>
+    <x v="65"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1587,11 +1874,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="3"/>
     <n v="385891"/>
-    <s v="天使"/>
+    <x v="66"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1599,11 +1887,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="4"/>
     <n v="385894"/>
-    <s v="我又初恋了"/>
+    <x v="67"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1611,11 +1900,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="5"/>
     <n v="385897"/>
-    <s v="香水"/>
+    <x v="68"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1623,11 +1913,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="6"/>
     <n v="385901"/>
-    <s v="摩托车日记"/>
+    <x v="69"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1635,11 +1926,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="7"/>
     <n v="385905"/>
-    <s v="最重要的小事"/>
+    <x v="70"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1647,11 +1939,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="8"/>
     <n v="385909"/>
-    <s v="快乐很伟大"/>
+    <x v="71"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1659,11 +1952,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="9"/>
     <n v="385913"/>
-    <s v="忘词"/>
+    <x v="72"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1671,11 +1965,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="10"/>
     <n v="385917"/>
-    <s v="宠上天"/>
+    <x v="73"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1683,11 +1978,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="11"/>
     <n v="385921"/>
-    <s v="米老鼠"/>
+    <x v="74"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1695,11 +1991,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="12"/>
     <n v="385925"/>
-    <s v="一千个世纪"/>
+    <x v="75"/>
     <x v="5"/>
     <n v="1"/>
     <n v="0"/>
@@ -1707,11 +2004,12 @@
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <s v="为爱而生"/>
+    <x v="5"/>
+    <s v="录音室专辑"/>
     <x v="5"/>
     <n v="13"/>
     <n v="385929"/>
-    <s v="胎音"/>
+    <x v="76"/>
     <x v="5"/>
     <n v="0"/>
     <n v="0"/>
@@ -1719,11 +2017,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
     <x v="6"/>
+    <s v="录音室专辑"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="385781"/>
-    <s v="突然好想你"/>
+    <x v="77"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1731,11 +2030,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="2"/>
     <n v="385784"/>
-    <s v="生存以上 生活以下"/>
+    <x v="78"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1743,11 +2043,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="3"/>
     <n v="385787"/>
-    <s v="你不是真正的快乐"/>
+    <x v="79"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1755,11 +2056,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="4"/>
     <n v="385789"/>
-    <s v="爆肝"/>
+    <x v="80"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1767,11 +2069,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="5"/>
     <n v="385791"/>
-    <s v="噢买尬"/>
+    <x v="81"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1779,11 +2082,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="6"/>
     <n v="385793"/>
-    <s v="出头天"/>
+    <x v="82"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1791,11 +2095,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="7"/>
     <n v="385795"/>
-    <s v="我心中尚未崩坏的地方"/>
+    <x v="83"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1803,11 +2108,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="8"/>
     <n v="385798"/>
-    <s v="春天的呐喊"/>
+    <x v="84"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1815,11 +2121,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="9"/>
     <n v="22198018"/>
-    <s v="夜访吸血鬼"/>
+    <x v="85"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1827,11 +2134,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="10"/>
     <n v="22198023"/>
-    <s v="如烟"/>
+    <x v="86"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1839,11 +2147,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="11"/>
     <n v="22198024"/>
-    <s v="后青春期的诗"/>
+    <x v="87"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1851,11 +2160,12 @@
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <s v="后青春期的诗"/>
+    <x v="6"/>
+    <s v="录音室专辑"/>
     <x v="6"/>
     <n v="12"/>
     <n v="22198025"/>
-    <s v="笑忘歌"/>
+    <x v="88"/>
     <x v="6"/>
     <n v="1"/>
     <n v="0"/>
@@ -1863,11 +2173,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
     <x v="7"/>
+    <s v="录音室专辑"/>
+    <x v="7"/>
     <n v="1"/>
     <n v="22196001"/>
-    <s v="有些事现在不做 一辈子都不会做了"/>
+    <x v="89"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1875,11 +2186,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="2"/>
     <n v="22196002"/>
-    <s v="我不愿让你一个人"/>
+    <x v="90"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1887,11 +2199,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="3"/>
     <n v="22197001"/>
-    <s v="星空"/>
+    <x v="91"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1899,11 +2212,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="4"/>
     <n v="22197003"/>
-    <s v="洗衣机"/>
+    <x v="92"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1911,11 +2225,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="5"/>
     <n v="22197004"/>
-    <s v="三个傻瓜"/>
+    <x v="93"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1923,11 +2238,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="6"/>
     <n v="22197005"/>
-    <s v="歪腰"/>
+    <x v="94"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1935,11 +2251,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="7"/>
     <n v="22197007"/>
-    <s v="干杯"/>
+    <x v="95"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1947,11 +2264,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="8"/>
     <n v="22197008"/>
-    <s v="仓颉"/>
+    <x v="96"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1959,11 +2277,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="9"/>
     <n v="22197009"/>
-    <n v="2012"/>
+    <x v="97"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1971,11 +2290,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="10"/>
     <n v="22197010"/>
-    <s v="第二人生"/>
+    <x v="98"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1983,11 +2303,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="11"/>
     <n v="22197011"/>
-    <s v="诺亚方舟"/>
+    <x v="99"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -1995,11 +2316,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="12"/>
     <n v="22197012"/>
-    <s v="明日"/>
+    <x v="100"/>
     <x v="7"/>
     <n v="0"/>
     <n v="0"/>
@@ -2007,11 +2329,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="13"/>
     <n v="22197014"/>
-    <s v="OAOA (现在就是永远)"/>
+    <x v="101"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -2019,11 +2342,12 @@
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <s v="第二人生 (明日版)"/>
+    <x v="7"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="14"/>
     <n v="2008204010"/>
-    <s v="T1213121"/>
+    <x v="102"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -2031,11 +2355,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="1"/>
     <n v="385542"/>
-    <n v="2012"/>
+    <x v="97"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2043,11 +2368,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="2"/>
     <n v="385544"/>
-    <s v="仓颉"/>
+    <x v="96"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2055,11 +2381,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="3"/>
     <n v="385547"/>
-    <s v="洗衣机"/>
+    <x v="92"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2067,11 +2394,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="4"/>
     <n v="385550"/>
-    <s v="歪腰"/>
+    <x v="94"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2079,11 +2407,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="5"/>
     <n v="385552"/>
-    <s v="干杯"/>
+    <x v="95"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2091,11 +2420,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="6"/>
     <n v="385554"/>
-    <s v="我不愿让你一个人"/>
+    <x v="90"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2103,11 +2433,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="7"/>
     <n v="385556"/>
-    <s v="星空"/>
+    <x v="91"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2115,11 +2446,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="8"/>
     <n v="385558"/>
-    <s v="三个傻瓜"/>
+    <x v="93"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2127,11 +2459,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="9"/>
     <n v="385561"/>
-    <s v="末日"/>
+    <x v="103"/>
     <x v="7"/>
     <n v="0"/>
     <n v="0"/>
@@ -2139,11 +2472,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="10"/>
     <n v="385563"/>
-    <s v="OAOA (丢掉名字性别)"/>
+    <x v="104"/>
     <x v="7"/>
     <n v="1"/>
     <n v="0"/>
@@ -2151,11 +2485,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="11"/>
     <n v="385565"/>
-    <s v="第二人生"/>
+    <x v="98"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2163,11 +2498,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="12"/>
     <n v="385566"/>
-    <s v="诺亚方舟"/>
+    <x v="99"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2175,11 +2511,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="13"/>
     <n v="385568"/>
-    <s v="有些事现在不做 一辈子都不会做了"/>
+    <x v="89"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2187,11 +2524,12 @@
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <s v="第二人生 (末日版)"/>
+    <x v="8"/>
+    <s v="录音室专辑"/>
     <x v="7"/>
     <n v="14"/>
     <n v="385576"/>
-    <s v="T1213121"/>
+    <x v="102"/>
     <x v="7"/>
     <n v="1"/>
     <n v="1"/>
@@ -2199,11 +2537,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="1"/>
     <n v="417953659"/>
-    <s v="如果我们不曾相遇"/>
+    <x v="105"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2211,11 +2550,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="2"/>
     <n v="422094252"/>
-    <s v="成名在望"/>
+    <x v="106"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2223,11 +2563,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="3"/>
     <n v="422094253"/>
-    <s v="好好 (想把你写成一首歌)"/>
+    <x v="107"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2235,11 +2576,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="4"/>
     <n v="422094254"/>
-    <s v="兄弟"/>
+    <x v="108"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2247,11 +2589,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="5"/>
     <n v="422104164"/>
-    <s v="人生有限公司"/>
+    <x v="109"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2259,11 +2602,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="6"/>
     <n v="422104138"/>
-    <s v="后来的我们"/>
+    <x v="110"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2271,11 +2615,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="7"/>
     <n v="422104166"/>
-    <s v="顽固"/>
+    <x v="111"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2283,11 +2628,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="8"/>
     <n v="417953658"/>
-    <s v="派对动物"/>
+    <x v="112"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2295,11 +2641,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="9"/>
     <n v="422104165"/>
-    <s v="最好的一天"/>
+    <x v="113"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2307,11 +2654,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="10"/>
     <n v="422094255"/>
-    <s v="少年他的奇幻漂流"/>
+    <x v="114"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2319,11 +2667,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="11"/>
     <n v="422104167"/>
-    <s v="终于结束的起点"/>
+    <x v="115"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2331,11 +2680,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="12"/>
     <n v="422094256"/>
-    <s v="任意门"/>
+    <x v="116"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2343,11 +2693,12 @@
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <s v="自传"/>
+    <x v="9"/>
+    <s v="录音室专辑"/>
     <x v="8"/>
     <n v="13"/>
     <n v="422094257"/>
-    <s v="转眼"/>
+    <x v="117"/>
     <x v="8"/>
     <n v="1"/>
     <n v="0"/>
@@ -2355,11 +2706,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="1"/>
     <n v="385965"/>
-    <s v="知足"/>
+    <x v="118"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2367,11 +2719,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="2"/>
     <n v="385967"/>
-    <s v="牙关"/>
+    <x v="119"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2379,11 +2732,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="3"/>
     <n v="385970"/>
-    <s v="乱世浮生"/>
+    <x v="120"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2391,11 +2745,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="4"/>
     <n v="385973"/>
-    <s v="恋爱ing"/>
+    <x v="121"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2403,11 +2758,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="5"/>
     <n v="385976"/>
-    <s v="听不到"/>
+    <x v="122"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2415,11 +2771,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="6"/>
     <n v="386021"/>
-    <s v="憨人"/>
+    <x v="17"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2427,11 +2784,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="7"/>
     <n v="385979"/>
-    <s v="拥抱"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2439,11 +2797,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="8"/>
     <n v="385981"/>
-    <s v="终结孤单"/>
+    <x v="13"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2451,11 +2810,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="9"/>
     <n v="385984"/>
-    <s v="而我知道"/>
+    <x v="40"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2463,11 +2823,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="10"/>
     <n v="385987"/>
-    <s v="孙悟空"/>
+    <x v="51"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2475,11 +2836,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="11"/>
     <n v="385990"/>
-    <s v="人生海海"/>
+    <x v="35"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2487,11 +2849,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="12"/>
     <n v="386032"/>
-    <s v="轧车"/>
+    <x v="6"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2499,11 +2862,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="13"/>
     <n v="385993"/>
-    <s v="疯狂世界"/>
+    <x v="0"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2511,11 +2875,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="14"/>
     <n v="386034"/>
-    <s v="I Love You 无望"/>
+    <x v="10"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2523,11 +2888,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="15"/>
     <n v="385996"/>
-    <s v="爱情万岁"/>
+    <x v="22"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2535,11 +2901,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="16"/>
     <n v="385999"/>
-    <s v="恒星的恒心"/>
+    <x v="37"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2547,11 +2914,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="17"/>
     <n v="386001"/>
-    <s v="温柔 (还你自由版)"/>
+    <x v="123"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2559,11 +2927,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="18"/>
     <n v="386005"/>
-    <s v="倔强"/>
+    <x v="52"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2571,11 +2940,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="19"/>
     <n v="386007"/>
-    <s v="金多虾"/>
+    <x v="124"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2583,11 +2953,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="20"/>
     <n v="386010"/>
-    <s v="麦来乱"/>
+    <x v="125"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2595,11 +2966,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="21"/>
     <n v="386011"/>
-    <s v="志明与春娇"/>
+    <x v="7"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2607,11 +2979,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="22"/>
     <n v="386014"/>
-    <s v="心中无别人"/>
+    <x v="15"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2619,11 +2992,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="23"/>
     <n v="386017"/>
-    <s v="好不好"/>
+    <x v="26"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2631,11 +3005,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="24"/>
     <n v="386025"/>
-    <s v="OK 啦"/>
+    <x v="126"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2643,11 +3018,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="25"/>
     <n v="386028"/>
-    <s v="垃圾车 (朋友版)"/>
+    <x v="127"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
@@ -2655,11 +3031,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="26"/>
     <n v="386030"/>
-    <s v="叫我第一名"/>
+    <x v="18"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2667,11 +3044,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="27"/>
     <n v="386035"/>
-    <s v="永远的永远"/>
+    <x v="30"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2679,11 +3057,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="28"/>
     <n v="386036"/>
-    <s v="借问众神明"/>
+    <x v="29"/>
     <x v="9"/>
     <n v="1"/>
     <n v="1"/>
@@ -2691,11 +3070,12 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="29"/>
     <n v="386038"/>
-    <s v="未来 (Sailing With Me)"/>
+    <x v="128"/>
     <x v="9"/>
     <n v="0"/>
     <n v="0"/>
@@ -2703,27 +3083,435 @@
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <s v="知足 最真杰作选"/>
+    <x v="10"/>
+    <s v="精选辑"/>
     <x v="9"/>
     <n v="30"/>
     <n v="386040"/>
-    <s v="咸鱼"/>
+    <x v="129"/>
     <x v="9"/>
     <n v="1"/>
     <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="28181103"/>
+    <x v="130"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="11"/>
+    <n v="2"/>
+    <n v="28181105"/>
+    <x v="131"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="12"/>
+    <n v="3"/>
+    <n v="28181107"/>
+    <x v="132"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="13"/>
+    <n v="4"/>
+    <n v="28181109"/>
+    <x v="133"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="14"/>
+    <n v="5"/>
+    <n v="28181111"/>
+    <x v="95"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="15"/>
+    <n v="6"/>
+    <n v="28181113"/>
+    <x v="134"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="16"/>
+    <n v="7"/>
+    <n v="28181115"/>
+    <x v="52"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="17"/>
+    <n v="8"/>
+    <n v="28181117"/>
+    <x v="77"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="18"/>
+    <n v="9"/>
+    <n v="28181119"/>
+    <x v="121"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="19"/>
+    <n v="10"/>
+    <n v="28181121"/>
+    <x v="135"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="20"/>
+    <n v="11"/>
+    <n v="28181123"/>
+    <x v="91"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="21"/>
+    <n v="12"/>
+    <n v="28181125"/>
+    <x v="90"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="22"/>
+    <n v="13"/>
+    <n v="28181127"/>
+    <x v="35"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="23"/>
+    <n v="14"/>
+    <n v="28181129"/>
+    <x v="136"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="24"/>
+    <n v="15"/>
+    <n v="28181131"/>
+    <x v="137"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="25"/>
+    <n v="16"/>
+    <n v="28181104"/>
+    <x v="138"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="26"/>
+    <n v="17"/>
+    <n v="28181106"/>
+    <x v="85"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="27"/>
+    <n v="18"/>
+    <n v="28181108"/>
+    <x v="86"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="28"/>
+    <n v="19"/>
+    <n v="28181110"/>
+    <x v="139"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="29"/>
+    <n v="20"/>
+    <n v="28181112"/>
+    <x v="24"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="30"/>
+    <n v="21"/>
+    <n v="28181114"/>
+    <x v="93"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="31"/>
+    <n v="22"/>
+    <n v="28181116"/>
+    <x v="51"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="32"/>
+    <n v="23"/>
+    <n v="28181118"/>
+    <x v="69"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="33"/>
+    <n v="24"/>
+    <n v="28181120"/>
+    <x v="70"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="34"/>
+    <n v="25"/>
+    <n v="28181122"/>
+    <x v="22"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="35"/>
+    <n v="26"/>
+    <n v="28181124"/>
+    <x v="38"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="36"/>
+    <n v="27"/>
+    <n v="28181126"/>
+    <x v="48"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="37"/>
+    <n v="28"/>
+    <n v="28181128"/>
+    <x v="99"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="38"/>
+    <n v="29"/>
+    <n v="28181130"/>
+    <x v="83"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="2740205"/>
+    <x v="11"/>
+    <s v="精选辑"/>
+    <x v="39"/>
+    <n v="30"/>
+    <n v="28181132"/>
+    <x v="17"/>
+    <x v="10"/>
+    <n v="1"/>
+    <n v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3979405A-18D3-674A-8872-87A46D648831}" name="数据透视表1" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F53B5E73-1E1B-C048-9495-86A00DE5D8A9}" name="数据透视表1" cacheId="52" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:C206" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+  <pivotFields count="14">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0">
+      <items count="13">
+        <item x="1"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" subtotalTop="0" showAll="0">
+      <items count="41">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -2734,14 +3522,188 @@
         <item x="6"/>
         <item x="7"/>
         <item x="8"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
+      <items count="141">
+        <item x="97"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item x="104"/>
+        <item x="101"/>
+        <item x="126"/>
+        <item x="28"/>
+        <item x="102"/>
+        <item x="39"/>
+        <item x="4"/>
+        <item x="22"/>
+        <item x="80"/>
+        <item x="42"/>
+        <item x="130"/>
+        <item x="31"/>
+        <item x="96"/>
+        <item x="60"/>
+        <item x="106"/>
+        <item x="73"/>
+        <item x="82"/>
+        <item x="84"/>
+        <item x="33"/>
+        <item x="38"/>
+        <item x="58"/>
+        <item x="98"/>
+        <item x="41"/>
+        <item x="40"/>
+        <item x="23"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="95"/>
+        <item x="17"/>
+        <item x="26"/>
+        <item x="107"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="37"/>
+        <item x="110"/>
+        <item x="87"/>
+        <item x="34"/>
+        <item x="57"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="124"/>
+        <item x="32"/>
+        <item x="43"/>
+        <item x="52"/>
+        <item x="71"/>
+        <item x="53"/>
+        <item x="127"/>
+        <item x="63"/>
+        <item x="135"/>
+        <item x="121"/>
+        <item x="120"/>
+        <item x="20"/>
+        <item x="125"/>
+        <item x="74"/>
+        <item x="14"/>
+        <item x="100"/>
+        <item x="69"/>
+        <item x="103"/>
+        <item x="25"/>
+        <item x="79"/>
+        <item x="138"/>
+        <item x="99"/>
+        <item x="81"/>
+        <item x="112"/>
+        <item x="64"/>
+        <item x="36"/>
+        <item x="55"/>
+        <item x="35"/>
+        <item x="109"/>
+        <item x="116"/>
+        <item x="105"/>
+        <item x="86"/>
+        <item x="134"/>
+        <item x="93"/>
+        <item x="132"/>
+        <item x="114"/>
+        <item x="61"/>
+        <item x="78"/>
+        <item x="3"/>
+        <item x="48"/>
+        <item x="62"/>
+        <item x="139"/>
+        <item x="45"/>
+        <item x="51"/>
+        <item x="76"/>
+        <item x="66"/>
+        <item x="122"/>
+        <item x="2"/>
+        <item x="77"/>
+        <item x="94"/>
+        <item x="111"/>
+        <item x="59"/>
+        <item x="49"/>
+        <item x="72"/>
+        <item x="65"/>
+        <item x="12"/>
+        <item x="128"/>
+        <item x="21"/>
+        <item x="137"/>
+        <item x="123"/>
+        <item x="90"/>
+        <item x="46"/>
+        <item x="83"/>
+        <item x="67"/>
+        <item x="44"/>
+        <item x="92"/>
+        <item x="129"/>
+        <item x="27"/>
+        <item x="68"/>
+        <item x="54"/>
+        <item x="50"/>
+        <item x="88"/>
+        <item x="15"/>
+        <item x="91"/>
+        <item x="108"/>
+        <item x="119"/>
+        <item x="133"/>
+        <item x="85"/>
+        <item x="24"/>
+        <item x="75"/>
+        <item x="1"/>
+        <item x="131"/>
+        <item x="30"/>
+        <item x="16"/>
+        <item x="89"/>
+        <item x="19"/>
+        <item x="56"/>
+        <item x="47"/>
+        <item x="6"/>
+        <item x="118"/>
+        <item x="136"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="115"/>
+        <item x="117"/>
+        <item x="113"/>
+        <item x="70"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0">
+      <items count="12">
         <item x="1"/>
         <item x="7"/>
         <item x="0"/>
@@ -2752,12 +3714,13 @@
         <item x="5"/>
         <item x="9"/>
         <item x="8"/>
+        <item x="10"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0">
       <items count="15">
         <item sd="0" x="0"/>
         <item sd="0" x="1"/>
@@ -2776,7 +3739,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0">
       <items count="7">
         <item sd="0" x="0"/>
         <item sd="0" x="1"/>
@@ -2787,7 +3750,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0">
       <items count="21">
         <item sd="0" x="0"/>
         <item sd="0" x="1"/>
@@ -2813,62 +3776,638 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="1">
+  <rowFields count="2">
+    <field x="2"/>
     <field x="7"/>
   </rowFields>
-  <rowItems count="11">
+  <rowItems count="203">
     <i>
       <x/>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i r="1">
+      <x v="54"/>
+    </i>
+    <i r="1">
+      <x v="57"/>
+    </i>
+    <i r="1">
+      <x v="98"/>
+    </i>
+    <i r="1">
+      <x v="100"/>
+    </i>
+    <i r="1">
+      <x v="115"/>
+    </i>
+    <i r="1">
+      <x v="126"/>
+    </i>
+    <i r="1">
+      <x v="128"/>
+    </i>
+    <i r="1">
+      <x v="135"/>
+    </i>
+    <i t="default">
+      <x/>
     </i>
     <i>
       <x v="1"/>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="51"/>
+    </i>
+    <i r="1">
+      <x v="52"/>
+    </i>
+    <i r="1">
+      <x v="59"/>
+    </i>
+    <i r="1">
+      <x v="63"/>
+    </i>
+    <i r="1">
+      <x v="64"/>
+    </i>
+    <i r="1">
+      <x v="70"/>
+    </i>
+    <i r="1">
+      <x v="74"/>
+    </i>
+    <i r="1">
+      <x v="75"/>
+    </i>
+    <i r="1">
+      <x v="76"/>
+    </i>
+    <i r="1">
+      <x v="77"/>
+    </i>
+    <i r="1">
+      <x v="82"/>
+    </i>
+    <i r="1">
+      <x v="84"/>
+    </i>
+    <i r="1">
+      <x v="86"/>
+    </i>
+    <i r="1">
+      <x v="91"/>
+    </i>
+    <i r="1">
+      <x v="101"/>
+    </i>
+    <i r="1">
+      <x v="103"/>
+    </i>
+    <i r="1">
+      <x v="105"/>
+    </i>
+    <i r="1">
+      <x v="116"/>
+    </i>
+    <i r="1">
+      <x v="119"/>
+    </i>
+    <i r="1">
+      <x v="120"/>
+    </i>
+    <i r="1">
+      <x v="121"/>
+    </i>
+    <i r="1">
+      <x v="124"/>
+    </i>
+    <i r="1">
+      <x v="133"/>
+    </i>
+    <i r="1">
+      <x v="139"/>
+    </i>
+    <i t="default">
+      <x v="1"/>
     </i>
     <i>
       <x v="2"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="58"/>
+    </i>
+    <i r="1">
+      <x v="64"/>
+    </i>
+    <i r="1">
+      <x v="76"/>
+    </i>
+    <i r="1">
+      <x v="92"/>
+    </i>
+    <i r="1">
+      <x v="103"/>
+    </i>
+    <i r="1">
+      <x v="108"/>
+    </i>
+    <i r="1">
+      <x v="116"/>
+    </i>
+    <i r="1">
+      <x v="127"/>
+    </i>
+    <i t="default">
+      <x v="2"/>
     </i>
     <i>
       <x v="3"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="60"/>
+    </i>
+    <i r="1">
+      <x v="64"/>
+    </i>
+    <i r="1">
+      <x v="76"/>
+    </i>
+    <i r="1">
+      <x v="92"/>
+    </i>
+    <i r="1">
+      <x v="103"/>
+    </i>
+    <i r="1">
+      <x v="108"/>
+    </i>
+    <i r="1">
+      <x v="116"/>
+    </i>
+    <i r="1">
+      <x v="127"/>
+    </i>
+    <i t="default">
+      <x v="3"/>
     </i>
     <i>
       <x v="4"/>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+    </i>
+    <i r="1">
+      <x v="81"/>
+    </i>
+    <i r="1">
+      <x v="90"/>
+    </i>
+    <i r="1">
+      <x v="123"/>
+    </i>
+    <i r="1">
+      <x v="131"/>
+    </i>
+    <i r="1">
+      <x v="134"/>
+    </i>
+    <i t="default">
+      <x v="4"/>
     </i>
     <i>
       <x v="5"/>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="38"/>
+    </i>
+    <i r="1">
+      <x v="62"/>
+    </i>
+    <i r="1">
+      <x v="65"/>
+    </i>
+    <i r="1">
+      <x v="74"/>
+    </i>
+    <i r="1">
+      <x v="80"/>
+    </i>
+    <i r="1">
+      <x v="91"/>
+    </i>
+    <i r="1">
+      <x v="105"/>
+    </i>
+    <i r="1">
+      <x v="114"/>
+    </i>
+    <i r="1">
+      <x v="120"/>
+    </i>
+    <i t="default">
+      <x v="5"/>
     </i>
     <i>
       <x v="6"/>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="42"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="61"/>
+    </i>
+    <i r="1">
+      <x v="70"/>
+    </i>
+    <i r="1">
+      <x v="110"/>
+    </i>
+    <i r="1">
+      <x v="121"/>
+    </i>
+    <i r="1">
+      <x v="125"/>
+    </i>
+    <i t="default">
+      <x v="6"/>
     </i>
     <i>
       <x v="7"/>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="48"/>
+    </i>
+    <i r="1">
+      <x v="50"/>
+    </i>
+    <i r="1">
+      <x v="69"/>
+    </i>
+    <i r="1">
+      <x v="79"/>
+    </i>
+    <i r="1">
+      <x v="83"/>
+    </i>
+    <i r="1">
+      <x v="86"/>
+    </i>
+    <i r="1">
+      <x v="94"/>
+    </i>
+    <i r="1">
+      <x v="112"/>
+    </i>
+    <i r="1">
+      <x v="129"/>
+    </i>
+    <i t="default">
+      <x v="7"/>
     </i>
     <i>
       <x v="8"/>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+    </i>
+    <i r="1">
+      <x v="68"/>
+    </i>
+    <i r="1">
+      <x v="82"/>
+    </i>
+    <i r="1">
+      <x v="85"/>
+    </i>
+    <i r="1">
+      <x v="95"/>
+    </i>
+    <i r="1">
+      <x v="104"/>
+    </i>
+    <i r="1">
+      <x v="107"/>
+    </i>
+    <i r="1">
+      <x v="113"/>
+    </i>
+    <i r="1">
+      <x v="130"/>
+    </i>
+    <i t="default">
+      <x v="8"/>
     </i>
     <i>
       <x v="9"/>
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+    </i>
+    <i r="1">
+      <x v="56"/>
+    </i>
+    <i r="1">
+      <x v="59"/>
+    </i>
+    <i r="1">
+      <x v="67"/>
+    </i>
+    <i r="1">
+      <x v="87"/>
+    </i>
+    <i r="1">
+      <x v="88"/>
+    </i>
+    <i r="1">
+      <x v="96"/>
+    </i>
+    <i r="1">
+      <x v="97"/>
+    </i>
+    <i r="1">
+      <x v="106"/>
+    </i>
+    <i r="1">
+      <x v="111"/>
+    </i>
+    <i r="1">
+      <x v="122"/>
+    </i>
+    <i r="1">
+      <x v="139"/>
+    </i>
+    <i t="default">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i r="1">
+      <x v="42"/>
+    </i>
+    <i r="1">
+      <x v="43"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+    </i>
+    <i r="1">
+      <x v="52"/>
+    </i>
+    <i r="1">
+      <x v="53"/>
+    </i>
+    <i r="1">
+      <x v="55"/>
+    </i>
+    <i r="1">
+      <x v="70"/>
+    </i>
+    <i r="1">
+      <x v="86"/>
+    </i>
+    <i r="1">
+      <x v="89"/>
+    </i>
+    <i r="1">
+      <x v="99"/>
+    </i>
+    <i r="1">
+      <x v="102"/>
+    </i>
+    <i r="1">
+      <x v="109"/>
+    </i>
+    <i r="1">
+      <x v="115"/>
+    </i>
+    <i r="1">
+      <x v="118"/>
+    </i>
+    <i r="1">
+      <x v="123"/>
+    </i>
+    <i r="1">
+      <x v="125"/>
+    </i>
+    <i r="1">
+      <x v="131"/>
+    </i>
+    <i r="1">
+      <x v="132"/>
+    </i>
+    <i r="1">
+      <x v="134"/>
+    </i>
+    <i r="1">
+      <x v="135"/>
+    </i>
+    <i t="default">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i r="1">
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="66"/>
+    </i>
+    <i r="1">
+      <x v="71"/>
+    </i>
+    <i r="1">
+      <x v="72"/>
+    </i>
+    <i r="1">
+      <x v="73"/>
+    </i>
+    <i r="1">
+      <x v="78"/>
+    </i>
+    <i r="1">
+      <x v="93"/>
+    </i>
+    <i r="1">
+      <x v="117"/>
+    </i>
+    <i r="1">
+      <x v="136"/>
+    </i>
+    <i r="1">
+      <x v="137"/>
+    </i>
+    <i r="1">
+      <x v="138"/>
+    </i>
+    <i t="default">
+      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <dataFields count="3">
-    <dataField name="计数项:song_name" fld="6" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="求和项:is_duplicate" fld="9" baseField="0" baseItem="0"/>
-    <dataField name="求和项:has_lyric" fld="8" baseField="0" baseItem="0"/>
+  <dataFields count="1">
+    <dataField name="计数项:album_name" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -2876,7 +4415,7 @@
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
+      <xpdl:pivotTableDefinition16 SubtotalsOnTopDefault="0"/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -3221,7 +4760,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -3256,7 +4795,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E2" s="2">
         <v>36348</v>
@@ -3291,7 +4830,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E3" s="2">
         <v>36348</v>
@@ -3326,7 +4865,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" s="2">
         <v>36348</v>
@@ -3361,7 +4900,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E5" s="2">
         <v>36348</v>
@@ -3396,7 +4935,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E6" s="2">
         <v>36348</v>
@@ -3431,7 +4970,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E7" s="2">
         <v>36348</v>
@@ -3466,7 +5005,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E8" s="2">
         <v>36348</v>
@@ -3501,7 +5040,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E9" s="2">
         <v>36348</v>
@@ -3536,7 +5075,7 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E10" s="2">
         <v>36348</v>
@@ -3571,7 +5110,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E11" s="2">
         <v>36348</v>
@@ -3606,7 +5145,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2">
         <v>36348</v>
@@ -3641,7 +5180,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E13" s="2">
         <v>36348</v>
@@ -3676,7 +5215,7 @@
         <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E14" s="2">
         <v>36714</v>
@@ -3711,7 +5250,7 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E15" s="2">
         <v>36714</v>
@@ -3746,7 +5285,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E16" s="2">
         <v>36714</v>
@@ -3781,7 +5320,7 @@
         <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E17" s="2">
         <v>36714</v>
@@ -3816,7 +5355,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E18" s="2">
         <v>36714</v>
@@ -3851,7 +5390,7 @@
         <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2">
         <v>36714</v>
@@ -3886,7 +5425,7 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E20" s="2">
         <v>36714</v>
@@ -3921,7 +5460,7 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E21" s="2">
         <v>36714</v>
@@ -3956,7 +5495,7 @@
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E22" s="2">
         <v>36714</v>
@@ -3991,7 +5530,7 @@
         <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E23" s="2">
         <v>36714</v>
@@ -4026,7 +5565,7 @@
         <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E24" s="2">
         <v>36714</v>
@@ -4061,7 +5600,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E25" s="2">
         <v>36714</v>
@@ -4096,7 +5635,7 @@
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E26" s="2">
         <v>37078</v>
@@ -4131,7 +5670,7 @@
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E27" s="2">
         <v>37078</v>
@@ -4166,7 +5705,7 @@
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E28" s="2">
         <v>37078</v>
@@ -4201,7 +5740,7 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E29" s="2">
         <v>37078</v>
@@ -4236,7 +5775,7 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E30" s="2">
         <v>37078</v>
@@ -4271,7 +5810,7 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E31" s="2">
         <v>37078</v>
@@ -4306,7 +5845,7 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E32" s="2">
         <v>37078</v>
@@ -4341,7 +5880,7 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E33" s="2">
         <v>37078</v>
@@ -4376,7 +5915,7 @@
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E34" s="2">
         <v>37078</v>
@@ -4411,7 +5950,7 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E35" s="2">
         <v>37078</v>
@@ -4446,7 +5985,7 @@
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E36" s="2">
         <v>37078</v>
@@ -4481,7 +6020,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E37" s="2">
         <v>37078</v>
@@ -4516,7 +6055,7 @@
         <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E38" s="2">
         <v>37936</v>
@@ -4551,7 +6090,7 @@
         <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E39" s="2">
         <v>37936</v>
@@ -4586,7 +6125,7 @@
         <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E40" s="2">
         <v>37936</v>
@@ -4621,7 +6160,7 @@
         <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E41" s="2">
         <v>37936</v>
@@ -4656,7 +6195,7 @@
         <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E42" s="2">
         <v>37936</v>
@@ -4691,7 +6230,7 @@
         <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E43" s="2">
         <v>37936</v>
@@ -4726,7 +6265,7 @@
         <v>60</v>
       </c>
       <c r="D44" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E44" s="2">
         <v>37936</v>
@@ -4761,7 +6300,7 @@
         <v>60</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E45" s="2">
         <v>37936</v>
@@ -4796,7 +6335,7 @@
         <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E46" s="2">
         <v>37936</v>
@@ -4831,7 +6370,7 @@
         <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E47" s="2">
         <v>37936</v>
@@ -4866,7 +6405,7 @@
         <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E48" s="2">
         <v>37936</v>
@@ -4901,7 +6440,7 @@
         <v>60</v>
       </c>
       <c r="D49" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E49" s="2">
         <v>37936</v>
@@ -4936,7 +6475,7 @@
         <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E50" s="2">
         <v>37936</v>
@@ -4971,7 +6510,7 @@
         <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E51" s="2">
         <v>37936</v>
@@ -5006,7 +6545,7 @@
         <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E52" s="2">
         <v>37936</v>
@@ -5041,7 +6580,7 @@
         <v>71</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E53" s="1">
         <v>38296</v>
@@ -5076,7 +6615,7 @@
         <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E54" s="1">
         <v>38296</v>
@@ -5111,7 +6650,7 @@
         <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E55" s="1">
         <v>38296</v>
@@ -5146,7 +6685,7 @@
         <v>71</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E56" s="1">
         <v>38296</v>
@@ -5181,7 +6720,7 @@
         <v>71</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E57" s="1">
         <v>38296</v>
@@ -5216,7 +6755,7 @@
         <v>71</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E58" s="1">
         <v>38296</v>
@@ -5251,7 +6790,7 @@
         <v>71</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E59" s="1">
         <v>38296</v>
@@ -5286,7 +6825,7 @@
         <v>71</v>
       </c>
       <c r="D60" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E60" s="1">
         <v>38296</v>
@@ -5321,7 +6860,7 @@
         <v>71</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E61" s="1">
         <v>38296</v>
@@ -5356,7 +6895,7 @@
         <v>71</v>
       </c>
       <c r="D62" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E62" s="1">
         <v>38296</v>
@@ -5391,7 +6930,7 @@
         <v>71</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E63" s="1">
         <v>38296</v>
@@ -5426,7 +6965,7 @@
         <v>71</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E64" s="1">
         <v>38296</v>
@@ -5461,7 +7000,7 @@
         <v>71</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E65" s="1">
         <v>38296</v>
@@ -5496,7 +7035,7 @@
         <v>89</v>
       </c>
       <c r="D66" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E66" s="2">
         <v>39080</v>
@@ -5531,7 +7070,7 @@
         <v>89</v>
       </c>
       <c r="D67" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E67" s="2">
         <v>39080</v>
@@ -5566,7 +7105,7 @@
         <v>89</v>
       </c>
       <c r="D68" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E68" s="2">
         <v>39080</v>
@@ -5601,7 +7140,7 @@
         <v>89</v>
       </c>
       <c r="D69" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E69" s="2">
         <v>39080</v>
@@ -5636,7 +7175,7 @@
         <v>89</v>
       </c>
       <c r="D70" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E70" s="2">
         <v>39080</v>
@@ -5671,7 +7210,7 @@
         <v>89</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E71" s="2">
         <v>39080</v>
@@ -5706,7 +7245,7 @@
         <v>89</v>
       </c>
       <c r="D72" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E72" s="2">
         <v>39080</v>
@@ -5741,7 +7280,7 @@
         <v>89</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E73" s="2">
         <v>39080</v>
@@ -5776,7 +7315,7 @@
         <v>89</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E74" s="2">
         <v>39080</v>
@@ -5811,7 +7350,7 @@
         <v>89</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E75" s="2">
         <v>39080</v>
@@ -5846,7 +7385,7 @@
         <v>89</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E76" s="2">
         <v>39080</v>
@@ -5881,7 +7420,7 @@
         <v>89</v>
       </c>
       <c r="D77" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E77" s="2">
         <v>39080</v>
@@ -5916,7 +7455,7 @@
         <v>89</v>
       </c>
       <c r="D78" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E78" s="2">
         <v>39080</v>
@@ -5951,7 +7490,7 @@
         <v>102</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E79" s="2">
         <v>39744</v>
@@ -5986,7 +7525,7 @@
         <v>102</v>
       </c>
       <c r="D80" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E80" s="2">
         <v>39744</v>
@@ -6021,7 +7560,7 @@
         <v>102</v>
       </c>
       <c r="D81" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E81" s="2">
         <v>39744</v>
@@ -6056,7 +7595,7 @@
         <v>102</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E82" s="2">
         <v>39744</v>
@@ -6091,7 +7630,7 @@
         <v>102</v>
       </c>
       <c r="D83" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E83" s="2">
         <v>39744</v>
@@ -6126,7 +7665,7 @@
         <v>102</v>
       </c>
       <c r="D84" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E84" s="2">
         <v>39744</v>
@@ -6161,7 +7700,7 @@
         <v>102</v>
       </c>
       <c r="D85" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E85" s="2">
         <v>39744</v>
@@ -6196,7 +7735,7 @@
         <v>102</v>
       </c>
       <c r="D86" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E86" s="2">
         <v>39744</v>
@@ -6231,7 +7770,7 @@
         <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E87" s="2">
         <v>39744</v>
@@ -6266,7 +7805,7 @@
         <v>102</v>
       </c>
       <c r="D88" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E88" s="2">
         <v>39744</v>
@@ -6301,7 +7840,7 @@
         <v>102</v>
       </c>
       <c r="D89" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E89" s="2">
         <v>39744</v>
@@ -6336,7 +7875,7 @@
         <v>102</v>
       </c>
       <c r="D90" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E90" s="2">
         <v>39744</v>
@@ -6371,7 +7910,7 @@
         <v>116</v>
       </c>
       <c r="D91" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E91" s="2">
         <v>40893</v>
@@ -6406,7 +7945,7 @@
         <v>116</v>
       </c>
       <c r="D92" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E92" s="2">
         <v>40893</v>
@@ -6441,7 +7980,7 @@
         <v>116</v>
       </c>
       <c r="D93" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E93" s="2">
         <v>40893</v>
@@ -6476,7 +8015,7 @@
         <v>116</v>
       </c>
       <c r="D94" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E94" s="2">
         <v>40893</v>
@@ -6511,7 +8050,7 @@
         <v>116</v>
       </c>
       <c r="D95" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E95" s="2">
         <v>40893</v>
@@ -6546,7 +8085,7 @@
         <v>116</v>
       </c>
       <c r="D96" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E96" s="2">
         <v>40893</v>
@@ -6581,7 +8120,7 @@
         <v>116</v>
       </c>
       <c r="D97" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E97" s="2">
         <v>40893</v>
@@ -6616,7 +8155,7 @@
         <v>116</v>
       </c>
       <c r="D98" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E98" s="2">
         <v>40893</v>
@@ -6651,7 +8190,7 @@
         <v>116</v>
       </c>
       <c r="D99" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E99" s="2">
         <v>40893</v>
@@ -6686,7 +8225,7 @@
         <v>116</v>
       </c>
       <c r="D100" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E100" s="2">
         <v>40893</v>
@@ -6721,7 +8260,7 @@
         <v>116</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E101" s="2">
         <v>40893</v>
@@ -6756,7 +8295,7 @@
         <v>116</v>
       </c>
       <c r="D102" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E102" s="2">
         <v>40893</v>
@@ -6791,7 +8330,7 @@
         <v>116</v>
       </c>
       <c r="D103" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E103" s="2">
         <v>40893</v>
@@ -6826,7 +8365,7 @@
         <v>116</v>
       </c>
       <c r="D104" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E104" s="2">
         <v>40893</v>
@@ -6861,7 +8400,7 @@
         <v>117</v>
       </c>
       <c r="D105" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E105" s="2">
         <v>40893</v>
@@ -6896,7 +8435,7 @@
         <v>117</v>
       </c>
       <c r="D106" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E106" s="2">
         <v>40893</v>
@@ -6931,7 +8470,7 @@
         <v>117</v>
       </c>
       <c r="D107" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E107" s="2">
         <v>40893</v>
@@ -6966,7 +8505,7 @@
         <v>117</v>
       </c>
       <c r="D108" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E108" s="2">
         <v>40893</v>
@@ -7001,7 +8540,7 @@
         <v>117</v>
       </c>
       <c r="D109" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E109" s="2">
         <v>40893</v>
@@ -7036,7 +8575,7 @@
         <v>117</v>
       </c>
       <c r="D110" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E110" s="2">
         <v>40893</v>
@@ -7071,7 +8610,7 @@
         <v>117</v>
       </c>
       <c r="D111" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E111" s="2">
         <v>40893</v>
@@ -7106,7 +8645,7 @@
         <v>117</v>
       </c>
       <c r="D112" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E112" s="2">
         <v>40893</v>
@@ -7141,7 +8680,7 @@
         <v>117</v>
       </c>
       <c r="D113" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E113" s="2">
         <v>40893</v>
@@ -7176,7 +8715,7 @@
         <v>117</v>
       </c>
       <c r="D114" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E114" s="2">
         <v>40893</v>
@@ -7211,7 +8750,7 @@
         <v>117</v>
       </c>
       <c r="D115" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E115" s="2">
         <v>40893</v>
@@ -7246,7 +8785,7 @@
         <v>117</v>
       </c>
       <c r="D116" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E116" s="2">
         <v>40893</v>
@@ -7281,7 +8820,7 @@
         <v>117</v>
       </c>
       <c r="D117" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E117" s="2">
         <v>40893</v>
@@ -7316,7 +8855,7 @@
         <v>117</v>
       </c>
       <c r="D118" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E118" s="2">
         <v>40893</v>
@@ -7351,7 +8890,7 @@
         <v>134</v>
       </c>
       <c r="D119" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E119" s="2">
         <v>42572</v>
@@ -7386,7 +8925,7 @@
         <v>134</v>
       </c>
       <c r="D120" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E120" s="2">
         <v>42572</v>
@@ -7421,7 +8960,7 @@
         <v>134</v>
       </c>
       <c r="D121" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E121" s="2">
         <v>42572</v>
@@ -7456,7 +8995,7 @@
         <v>134</v>
       </c>
       <c r="D122" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E122" s="2">
         <v>42572</v>
@@ -7491,7 +9030,7 @@
         <v>134</v>
       </c>
       <c r="D123" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E123" s="2">
         <v>42572</v>
@@ -7526,7 +9065,7 @@
         <v>134</v>
       </c>
       <c r="D124" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E124" s="2">
         <v>42572</v>
@@ -7561,7 +9100,7 @@
         <v>134</v>
       </c>
       <c r="D125" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E125" s="2">
         <v>42572</v>
@@ -7596,7 +9135,7 @@
         <v>134</v>
       </c>
       <c r="D126" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E126" s="2">
         <v>42572</v>
@@ -7631,7 +9170,7 @@
         <v>134</v>
       </c>
       <c r="D127" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E127" s="2">
         <v>42572</v>
@@ -7666,7 +9205,7 @@
         <v>134</v>
       </c>
       <c r="D128" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E128" s="2">
         <v>42572</v>
@@ -7701,7 +9240,7 @@
         <v>134</v>
       </c>
       <c r="D129" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E129" s="2">
         <v>42572</v>
@@ -7736,7 +9275,7 @@
         <v>134</v>
       </c>
       <c r="D130" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E130" s="2">
         <v>42572</v>
@@ -7771,7 +9310,7 @@
         <v>134</v>
       </c>
       <c r="D131" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E131" s="2">
         <v>42572</v>
@@ -7806,7 +9345,7 @@
         <v>145</v>
       </c>
       <c r="D132" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E132" s="2">
         <v>38590</v>
@@ -7841,7 +9380,7 @@
         <v>145</v>
       </c>
       <c r="D133" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E133" s="2">
         <v>38590</v>
@@ -7876,7 +9415,7 @@
         <v>145</v>
       </c>
       <c r="D134" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E134" s="2">
         <v>38590</v>
@@ -7911,7 +9450,7 @@
         <v>145</v>
       </c>
       <c r="D135" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E135" s="2">
         <v>38590</v>
@@ -7946,7 +9485,7 @@
         <v>145</v>
       </c>
       <c r="D136" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E136" s="2">
         <v>38590</v>
@@ -7981,7 +9520,7 @@
         <v>145</v>
       </c>
       <c r="D137" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E137" s="2">
         <v>38590</v>
@@ -8016,7 +9555,7 @@
         <v>145</v>
       </c>
       <c r="D138" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E138" s="2">
         <v>38590</v>
@@ -8051,7 +9590,7 @@
         <v>145</v>
       </c>
       <c r="D139" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E139" s="2">
         <v>38590</v>
@@ -8086,7 +9625,7 @@
         <v>145</v>
       </c>
       <c r="D140" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E140" s="2">
         <v>38590</v>
@@ -8121,7 +9660,7 @@
         <v>145</v>
       </c>
       <c r="D141" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E141" s="2">
         <v>38590</v>
@@ -8156,7 +9695,7 @@
         <v>145</v>
       </c>
       <c r="D142" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E142" s="2">
         <v>38590</v>
@@ -8191,7 +9730,7 @@
         <v>145</v>
       </c>
       <c r="D143" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E143" s="2">
         <v>38590</v>
@@ -8226,7 +9765,7 @@
         <v>145</v>
       </c>
       <c r="D144" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E144" s="2">
         <v>38590</v>
@@ -8261,7 +9800,7 @@
         <v>145</v>
       </c>
       <c r="D145" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E145" s="2">
         <v>38590</v>
@@ -8296,7 +9835,7 @@
         <v>145</v>
       </c>
       <c r="D146" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E146" s="2">
         <v>38590</v>
@@ -8331,7 +9870,7 @@
         <v>145</v>
       </c>
       <c r="D147" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E147" s="2">
         <v>38590</v>
@@ -8366,7 +9905,7 @@
         <v>145</v>
       </c>
       <c r="D148" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E148" s="2">
         <v>38590</v>
@@ -8401,7 +9940,7 @@
         <v>145</v>
       </c>
       <c r="D149" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E149" s="2">
         <v>38590</v>
@@ -8436,7 +9975,7 @@
         <v>145</v>
       </c>
       <c r="D150" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E150" s="2">
         <v>38590</v>
@@ -8471,7 +10010,7 @@
         <v>145</v>
       </c>
       <c r="D151" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E151" s="2">
         <v>38590</v>
@@ -8506,7 +10045,7 @@
         <v>145</v>
       </c>
       <c r="D152" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E152" s="2">
         <v>38590</v>
@@ -8541,7 +10080,7 @@
         <v>145</v>
       </c>
       <c r="D153" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E153" s="2">
         <v>38590</v>
@@ -8576,7 +10115,7 @@
         <v>145</v>
       </c>
       <c r="D154" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E154" s="2">
         <v>38590</v>
@@ -8611,7 +10150,7 @@
         <v>145</v>
       </c>
       <c r="D155" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E155" s="2">
         <v>38590</v>
@@ -8646,7 +10185,7 @@
         <v>145</v>
       </c>
       <c r="D156" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E156" s="2">
         <v>38590</v>
@@ -8681,7 +10220,7 @@
         <v>145</v>
       </c>
       <c r="D157" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E157" s="2">
         <v>38590</v>
@@ -8716,7 +10255,7 @@
         <v>145</v>
       </c>
       <c r="D158" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E158" s="2">
         <v>38590</v>
@@ -8751,7 +10290,7 @@
         <v>145</v>
       </c>
       <c r="D159" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E159" s="2">
         <v>38590</v>
@@ -8786,7 +10325,7 @@
         <v>145</v>
       </c>
       <c r="D160" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E160" s="2">
         <v>38590</v>
@@ -8821,7 +10360,7 @@
         <v>145</v>
       </c>
       <c r="D161" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E161" s="2">
         <v>38590</v>
@@ -8853,10 +10392,10 @@
         <v>2740205</v>
       </c>
       <c r="C162" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D162" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E162" s="2">
         <v>41638</v>
@@ -8868,10 +10407,10 @@
         <v>28181103</v>
       </c>
       <c r="H162" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I162" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -8888,13 +10427,13 @@
         <v>2740205</v>
       </c>
       <c r="C163" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D163" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E163" s="2">
-        <v>41639</v>
+        <v>41638</v>
       </c>
       <c r="F163">
         <v>2</v>
@@ -8903,10 +10442,10 @@
         <v>28181105</v>
       </c>
       <c r="H163" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I163" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J163">
         <v>1</v>
@@ -8923,13 +10462,13 @@
         <v>2740205</v>
       </c>
       <c r="C164" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D164" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E164" s="2">
-        <v>41640</v>
+        <v>41638</v>
       </c>
       <c r="F164">
         <v>3</v>
@@ -8938,10 +10477,10 @@
         <v>28181107</v>
       </c>
       <c r="H164" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I164" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J164">
         <v>1</v>
@@ -8958,13 +10497,13 @@
         <v>2740205</v>
       </c>
       <c r="C165" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D165" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E165" s="2">
-        <v>41641</v>
+        <v>41638</v>
       </c>
       <c r="F165">
         <v>4</v>
@@ -8973,10 +10512,10 @@
         <v>28181109</v>
       </c>
       <c r="H165" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I165" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J165">
         <v>1</v>
@@ -8993,13 +10532,13 @@
         <v>2740205</v>
       </c>
       <c r="C166" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D166" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E166" s="2">
-        <v>41642</v>
+        <v>41638</v>
       </c>
       <c r="F166">
         <v>5</v>
@@ -9011,7 +10550,7 @@
         <v>109</v>
       </c>
       <c r="I166" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -9028,13 +10567,13 @@
         <v>2740205</v>
       </c>
       <c r="C167" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D167" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E167" s="2">
-        <v>41643</v>
+        <v>41638</v>
       </c>
       <c r="F167">
         <v>6</v>
@@ -9043,10 +10582,10 @@
         <v>28181113</v>
       </c>
       <c r="H167" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I167" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J167">
         <v>1</v>
@@ -9063,13 +10602,13 @@
         <v>2740205</v>
       </c>
       <c r="C168" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D168" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E168" s="2">
-        <v>41644</v>
+        <v>41638</v>
       </c>
       <c r="F168">
         <v>7</v>
@@ -9081,7 +10620,7 @@
         <v>62</v>
       </c>
       <c r="I168" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J168">
         <v>1</v>
@@ -9098,13 +10637,13 @@
         <v>2740205</v>
       </c>
       <c r="C169" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D169" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E169" s="2">
-        <v>41645</v>
+        <v>41638</v>
       </c>
       <c r="F169">
         <v>8</v>
@@ -9116,7 +10655,7 @@
         <v>90</v>
       </c>
       <c r="I169" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J169">
         <v>1</v>
@@ -9133,13 +10672,13 @@
         <v>2740205</v>
       </c>
       <c r="C170" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D170" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E170" s="2">
-        <v>41646</v>
+        <v>41638</v>
       </c>
       <c r="F170">
         <v>9</v>
@@ -9151,7 +10690,7 @@
         <v>138</v>
       </c>
       <c r="I170" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J170">
         <v>1</v>
@@ -9168,13 +10707,13 @@
         <v>2740205</v>
       </c>
       <c r="C171" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D171" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E171" s="2">
-        <v>41647</v>
+        <v>41638</v>
       </c>
       <c r="F171">
         <v>10</v>
@@ -9183,10 +10722,10 @@
         <v>28181121</v>
       </c>
       <c r="H171" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I171" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J171">
         <v>1</v>
@@ -9203,13 +10742,13 @@
         <v>2740205</v>
       </c>
       <c r="C172" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D172" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E172" s="2">
-        <v>41648</v>
+        <v>41638</v>
       </c>
       <c r="F172">
         <v>11</v>
@@ -9221,7 +10760,7 @@
         <v>105</v>
       </c>
       <c r="I172" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J172">
         <v>1</v>
@@ -9238,13 +10777,13 @@
         <v>2740205</v>
       </c>
       <c r="C173" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D173" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E173" s="2">
-        <v>41649</v>
+        <v>41638</v>
       </c>
       <c r="F173">
         <v>12</v>
@@ -9256,7 +10795,7 @@
         <v>104</v>
       </c>
       <c r="I173" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J173">
         <v>1</v>
@@ -9273,13 +10812,13 @@
         <v>2740205</v>
       </c>
       <c r="C174" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D174" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E174" s="2">
-        <v>41650</v>
+        <v>41638</v>
       </c>
       <c r="F174">
         <v>13</v>
@@ -9291,7 +10830,7 @@
         <v>43</v>
       </c>
       <c r="I174" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J174">
         <v>1</v>
@@ -9308,13 +10847,13 @@
         <v>2740205</v>
       </c>
       <c r="C175" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D175" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E175" s="2">
-        <v>41651</v>
+        <v>41638</v>
       </c>
       <c r="F175">
         <v>14</v>
@@ -9323,10 +10862,10 @@
         <v>28181129</v>
       </c>
       <c r="H175" t="s">
+        <v>160</v>
+      </c>
+      <c r="I175" t="s">
         <v>164</v>
-      </c>
-      <c r="I175" t="s">
-        <v>168</v>
       </c>
       <c r="J175">
         <v>1</v>
@@ -9343,13 +10882,13 @@
         <v>2740205</v>
       </c>
       <c r="C176" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D176" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E176" s="2">
-        <v>41652</v>
+        <v>41638</v>
       </c>
       <c r="F176">
         <v>15</v>
@@ -9358,10 +10897,10 @@
         <v>28181131</v>
       </c>
       <c r="H176" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I176" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J176">
         <v>1</v>
@@ -9378,13 +10917,13 @@
         <v>2740205</v>
       </c>
       <c r="C177" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D177" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E177" s="2">
-        <v>41653</v>
+        <v>41638</v>
       </c>
       <c r="F177">
         <v>16</v>
@@ -9393,10 +10932,10 @@
         <v>28181104</v>
       </c>
       <c r="H177" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I177" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J177">
         <v>1</v>
@@ -9413,13 +10952,13 @@
         <v>2740205</v>
       </c>
       <c r="C178" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D178" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E178" s="2">
-        <v>41654</v>
+        <v>41638</v>
       </c>
       <c r="F178">
         <v>17</v>
@@ -9431,7 +10970,7 @@
         <v>98</v>
       </c>
       <c r="I178" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J178">
         <v>1</v>
@@ -9448,13 +10987,13 @@
         <v>2740205</v>
       </c>
       <c r="C179" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D179" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E179" s="2">
-        <v>41655</v>
+        <v>41638</v>
       </c>
       <c r="F179">
         <v>18</v>
@@ -9466,7 +11005,7 @@
         <v>99</v>
       </c>
       <c r="I179" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J179">
         <v>1</v>
@@ -9483,13 +11022,13 @@
         <v>2740205</v>
       </c>
       <c r="C180" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D180" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E180" s="2">
-        <v>41656</v>
+        <v>41638</v>
       </c>
       <c r="F180">
         <v>19</v>
@@ -9498,10 +11037,10 @@
         <v>28181110</v>
       </c>
       <c r="H180" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I180" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J180">
         <v>1</v>
@@ -9518,13 +11057,13 @@
         <v>2740205</v>
       </c>
       <c r="C181" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D181" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E181" s="2">
-        <v>41657</v>
+        <v>41638</v>
       </c>
       <c r="F181">
         <v>20</v>
@@ -9536,7 +11075,7 @@
         <v>32</v>
       </c>
       <c r="I181" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J181">
         <v>1</v>
@@ -9553,13 +11092,13 @@
         <v>2740205</v>
       </c>
       <c r="C182" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D182" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E182" s="2">
-        <v>41658</v>
+        <v>41638</v>
       </c>
       <c r="F182">
         <v>21</v>
@@ -9571,7 +11110,7 @@
         <v>107</v>
       </c>
       <c r="I182" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J182">
         <v>1</v>
@@ -9588,13 +11127,13 @@
         <v>2740205</v>
       </c>
       <c r="C183" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D183" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E183" s="2">
-        <v>41659</v>
+        <v>41638</v>
       </c>
       <c r="F183">
         <v>22</v>
@@ -9606,7 +11145,7 @@
         <v>61</v>
       </c>
       <c r="I183" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J183">
         <v>1</v>
@@ -9623,13 +11162,13 @@
         <v>2740205</v>
       </c>
       <c r="C184" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D184" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E184" s="2">
-        <v>41660</v>
+        <v>41638</v>
       </c>
       <c r="F184">
         <v>23</v>
@@ -9641,7 +11180,7 @@
         <v>81</v>
       </c>
       <c r="I184" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J184">
         <v>1</v>
@@ -9658,13 +11197,13 @@
         <v>2740205</v>
       </c>
       <c r="C185" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D185" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E185" s="2">
-        <v>41661</v>
+        <v>41638</v>
       </c>
       <c r="F185">
         <v>24</v>
@@ -9676,7 +11215,7 @@
         <v>82</v>
       </c>
       <c r="I185" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J185">
         <v>1</v>
@@ -9693,13 +11232,13 @@
         <v>2740205</v>
       </c>
       <c r="C186" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D186" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E186" s="2">
-        <v>41662</v>
+        <v>41638</v>
       </c>
       <c r="F186">
         <v>25</v>
@@ -9711,7 +11250,7 @@
         <v>30</v>
       </c>
       <c r="I186" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J186">
         <v>1</v>
@@ -9728,13 +11267,13 @@
         <v>2740205</v>
       </c>
       <c r="C187" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D187" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E187" s="2">
-        <v>41663</v>
+        <v>41638</v>
       </c>
       <c r="F187">
         <v>26</v>
@@ -9746,7 +11285,7 @@
         <v>47</v>
       </c>
       <c r="I187" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J187">
         <v>1</v>
@@ -9763,13 +11302,13 @@
         <v>2740205</v>
       </c>
       <c r="C188" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D188" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E188" s="2">
-        <v>41664</v>
+        <v>41638</v>
       </c>
       <c r="F188">
         <v>27</v>
@@ -9781,7 +11320,7 @@
         <v>57</v>
       </c>
       <c r="I188" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J188">
         <v>1</v>
@@ -9798,13 +11337,13 @@
         <v>2740205</v>
       </c>
       <c r="C189" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D189" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E189" s="2">
-        <v>41665</v>
+        <v>41638</v>
       </c>
       <c r="F189">
         <v>28</v>
@@ -9816,7 +11355,7 @@
         <v>112</v>
       </c>
       <c r="I189" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J189">
         <v>1</v>
@@ -9833,13 +11372,13 @@
         <v>2740205</v>
       </c>
       <c r="C190" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D190" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E190" s="2">
-        <v>41666</v>
+        <v>41638</v>
       </c>
       <c r="F190">
         <v>29</v>
@@ -9851,7 +11390,7 @@
         <v>96</v>
       </c>
       <c r="I190" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J190">
         <v>1</v>
@@ -9868,13 +11407,13 @@
         <v>2740205</v>
       </c>
       <c r="C191" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D191" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E191" s="2">
-        <v>41667</v>
+        <v>41638</v>
       </c>
       <c r="F191">
         <v>30</v>
@@ -9886,7 +11425,7 @@
         <v>25</v>
       </c>
       <c r="I191" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J191">
         <v>1</v>
@@ -9904,40 +11443,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7089906A-4084-CE42-A748-343F53CDD52F}">
-  <dimension ref="A3:D14"/>
+  <dimension ref="A3:C206"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="12" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="21" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="8" bestFit="1" customWidth="1"/>
     <col min="42" max="43" width="12" bestFit="1" customWidth="1"/>
     <col min="44" max="46" width="8" bestFit="1" customWidth="1"/>
@@ -10013,172 +11557,1675 @@
     <col min="132" max="132" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="B18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="B23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="B30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="B32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="B34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="B37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="B40" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="B41" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="B44" t="s">
+        <v>155</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="B45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="B46" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48">
+        <v>2012</v>
+      </c>
+      <c r="C48" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="B49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="B50" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="B52" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="B54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="B55" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="B58" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="B59" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="B60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="B61" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>169</v>
+      </c>
+      <c r="C62" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63">
+        <v>2012</v>
+      </c>
+      <c r="C63" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="B65" t="s">
+        <v>115</v>
+      </c>
+      <c r="C65" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="B66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="B67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C67" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="B68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="B69" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="B71" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="B72" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="B73" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="B74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="B75" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="B76" t="s">
+        <v>103</v>
+      </c>
+      <c r="C76" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="B84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>171</v>
+      </c>
+      <c r="C90" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>100</v>
+      </c>
+      <c r="B91" t="s">
+        <v>93</v>
+      </c>
+      <c r="C91" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="B92" t="s">
+        <v>95</v>
+      </c>
+      <c r="C92" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="B93" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="B94" t="s">
+        <v>100</v>
+      </c>
+      <c r="C94" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="B95" t="s">
+        <v>92</v>
+      </c>
+      <c r="C95" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="B96" t="s">
+        <v>94</v>
+      </c>
+      <c r="C96" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="B97" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="B98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C98" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="B99" t="s">
+        <v>90</v>
+      </c>
+      <c r="C99" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="B100" t="s">
+        <v>96</v>
+      </c>
+      <c r="C100" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="B101" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="B102" t="s">
+        <v>98</v>
+      </c>
+      <c r="C102" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>172</v>
+      </c>
+      <c r="C103" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>43</v>
+      </c>
+      <c r="B104" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="B105" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="B106" t="s">
+        <v>41</v>
+      </c>
+      <c r="C106" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="B107" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="B108" t="s">
+        <v>42</v>
+      </c>
+      <c r="C108" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="B109" t="s">
+        <v>37</v>
+      </c>
+      <c r="C109" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="B110" t="s">
+        <v>40</v>
+      </c>
+      <c r="C110" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="B111" t="s">
+        <v>33</v>
+      </c>
+      <c r="C111" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="B112" t="s">
+        <v>43</v>
+      </c>
+      <c r="C112" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="B113" t="s">
+        <v>35</v>
+      </c>
+      <c r="C113" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="B114" t="s">
+        <v>32</v>
+      </c>
+      <c r="C114" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="B115" t="s">
+        <v>38</v>
+      </c>
+      <c r="C115" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>173</v>
+      </c>
+      <c r="C116" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>71</v>
+      </c>
+      <c r="B117" t="s">
+        <v>70</v>
+      </c>
+      <c r="C117" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="B118" t="s">
+        <v>68</v>
+      </c>
+      <c r="C118" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="B119" t="s">
+        <v>67</v>
+      </c>
+      <c r="C119" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="B120" t="s">
+        <v>62</v>
+      </c>
+      <c r="C120" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="B121" t="s">
+        <v>63</v>
+      </c>
+      <c r="C121" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="B122" t="s">
+        <v>73</v>
+      </c>
+      <c r="C122" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="B123" t="s">
+        <v>65</v>
+      </c>
+      <c r="C123" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="B124" t="s">
+        <v>71</v>
+      </c>
+      <c r="C124" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="B125" t="s">
+        <v>72</v>
+      </c>
+      <c r="C125" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="B126" t="s">
+        <v>61</v>
+      </c>
+      <c r="C126" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="B127" t="s">
+        <v>69</v>
+      </c>
+      <c r="C127" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="B128" t="s">
+        <v>64</v>
+      </c>
+      <c r="C128" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="B129" t="s">
+        <v>66</v>
+      </c>
+      <c r="C129" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>174</v>
+      </c>
+      <c r="C130" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>54</v>
+      </c>
+      <c r="B131" t="s">
+        <v>48</v>
+      </c>
+      <c r="C131" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="B132" t="s">
+        <v>51</v>
+      </c>
+      <c r="C132" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="B133" t="s">
+        <v>47</v>
+      </c>
+      <c r="C133" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="B134" t="s">
+        <v>50</v>
+      </c>
+      <c r="C134" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="B135" t="s">
+        <v>49</v>
+      </c>
+      <c r="C135" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="B136" t="s">
+        <v>46</v>
+      </c>
+      <c r="C136" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="B137" t="s">
+        <v>52</v>
+      </c>
+      <c r="C137" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="B138" t="s">
+        <v>45</v>
+      </c>
+      <c r="C138" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="B139" t="s">
+        <v>57</v>
+      </c>
+      <c r="C139" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="B140" t="s">
+        <v>54</v>
+      </c>
+      <c r="C140" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="B141" t="s">
+        <v>58</v>
+      </c>
+      <c r="C141" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="B142" t="s">
+        <v>55</v>
+      </c>
+      <c r="C142" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="B143" t="s">
+        <v>53</v>
+      </c>
+      <c r="C143" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="B144" t="s">
+        <v>59</v>
+      </c>
+      <c r="C144" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="B145" t="s">
+        <v>56</v>
+      </c>
+      <c r="C145" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>175</v>
+      </c>
+      <c r="C146" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>77</v>
+      </c>
+      <c r="B147" t="s">
+        <v>85</v>
+      </c>
+      <c r="C147" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="B148" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="B149" t="s">
+        <v>86</v>
+      </c>
+      <c r="C149" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="B150" t="s">
+        <v>81</v>
+      </c>
+      <c r="C150" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="B151" t="s">
+        <v>76</v>
+      </c>
+      <c r="C151" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="B152" t="s">
+        <v>88</v>
+      </c>
+      <c r="C152" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="B153" t="s">
+        <v>78</v>
+      </c>
+      <c r="C153" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="B154" t="s">
+        <v>84</v>
+      </c>
+      <c r="C154" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="B155" t="s">
+        <v>77</v>
+      </c>
+      <c r="C155" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="B156" t="s">
+        <v>79</v>
+      </c>
+      <c r="C156" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="B157" t="s">
+        <v>80</v>
+      </c>
+      <c r="C157" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="B158" t="s">
+        <v>87</v>
+      </c>
+      <c r="C158" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="B159" t="s">
+        <v>82</v>
+      </c>
+      <c r="C159" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
+        <v>176</v>
+      </c>
+      <c r="C160" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>145</v>
+      </c>
+      <c r="B161" t="s">
+        <v>18</v>
+      </c>
+      <c r="C161" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="B162" t="s">
+        <v>141</v>
+      </c>
+      <c r="C162" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="B163" t="s">
+        <v>30</v>
+      </c>
+      <c r="C163" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="B164" t="s">
+        <v>49</v>
+      </c>
+      <c r="C164" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="B165" t="s">
+        <v>8</v>
+      </c>
+      <c r="C165" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="B166" t="s">
+        <v>25</v>
+      </c>
+      <c r="C166" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="B167" t="s">
+        <v>34</v>
+      </c>
+      <c r="C167" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="B168" t="s">
+        <v>46</v>
+      </c>
+      <c r="C168" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="B169" t="s">
+        <v>26</v>
+      </c>
+      <c r="C169" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="B170" t="s">
+        <v>37</v>
+      </c>
+      <c r="C170" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="B171" t="s">
+        <v>139</v>
+      </c>
+      <c r="C171" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="B172" t="s">
+        <v>62</v>
+      </c>
+      <c r="C172" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="B173" t="s">
+        <v>142</v>
+      </c>
+      <c r="C173" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="B174" t="s">
+        <v>138</v>
+      </c>
+      <c r="C174" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="B175" t="s">
+        <v>137</v>
+      </c>
+      <c r="C175" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="B176" t="s">
+        <v>140</v>
+      </c>
+      <c r="C176" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="B177" t="s">
+        <v>43</v>
+      </c>
+      <c r="C177" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="B178" t="s">
+        <v>61</v>
+      </c>
+      <c r="C178" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="B179" t="s">
+        <v>74</v>
+      </c>
+      <c r="C179" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="B180" t="s">
+        <v>143</v>
+      </c>
+      <c r="C180" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="B181" t="s">
+        <v>75</v>
+      </c>
+      <c r="C181" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="B182" t="s">
+        <v>144</v>
+      </c>
+      <c r="C182" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="B183" t="s">
+        <v>23</v>
+      </c>
+      <c r="C183" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="B184" t="s">
+        <v>136</v>
+      </c>
+      <c r="C184" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="B185" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="B186" t="s">
+        <v>38</v>
+      </c>
+      <c r="C186" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="B187" t="s">
+        <v>14</v>
+      </c>
+      <c r="C187" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="B188" t="s">
+        <v>135</v>
+      </c>
+      <c r="C188" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="B189" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="B190" t="s">
+        <v>21</v>
+      </c>
+      <c r="C190" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
+        <v>177</v>
+      </c>
+      <c r="C191" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
+        <v>133</v>
+      </c>
+      <c r="B192" t="s">
+        <v>121</v>
+      </c>
+      <c r="C192" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="B193" t="s">
+        <v>122</v>
+      </c>
+      <c r="C193" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="B194" t="s">
+        <v>125</v>
+      </c>
+      <c r="C194" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="B195" t="s">
+        <v>127</v>
+      </c>
+      <c r="C195" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="B196" t="s">
+        <v>124</v>
+      </c>
+      <c r="C196" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="B197" t="s">
+        <v>131</v>
+      </c>
+      <c r="C197" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="B198" t="s">
+        <v>120</v>
+      </c>
+      <c r="C198" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="B199" t="s">
+        <v>129</v>
+      </c>
+      <c r="C199" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="B200" t="s">
+        <v>126</v>
+      </c>
+      <c r="C200" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="B201" t="s">
+        <v>123</v>
+      </c>
+      <c r="C201" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="B202" t="s">
+        <v>130</v>
+      </c>
+      <c r="C202" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="B203" t="s">
+        <v>132</v>
+      </c>
+      <c r="C203" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="B204" t="s">
+        <v>128</v>
+      </c>
+      <c r="C204" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
+        <v>178</v>
+      </c>
+      <c r="C205" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
         <v>150</v>
       </c>
-      <c r="B3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12">
-        <v>30</v>
-      </c>
-      <c r="C12">
-        <v>18</v>
-      </c>
-      <c r="D12">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13">
-        <v>13</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14">
-        <v>160</v>
-      </c>
-      <c r="C14">
-        <v>30</v>
-      </c>
-      <c r="D14">
-        <v>154</v>
+      <c r="C206" s="5">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/songs/mayday/data/mayday_songs.xlsx
+++ b/songs/mayday/data/mayday_songs.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1/Code/net_charts/songs/mayday/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225F6BEF-F0E0-CF42-82F2-BEFC019E9E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBAB643-C777-804B-A95E-7FCF19F2FEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8380" yWindow="600" windowWidth="28100" windowHeight="17360" xr2:uid="{83F95A99-0641-214A-BFE5-EC231FCA42BA}"/>
+    <workbookView xWindow="15940" yWindow="600" windowWidth="28100" windowHeight="17360" xr2:uid="{83F95A99-0641-214A-BFE5-EC231FCA42BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$191</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="52" r:id="rId3"/>
+    <pivotCache cacheId="58" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="167">
   <si>
     <t>album_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -526,9 +529,6 @@
     <t>步步</t>
   </si>
   <si>
-    <t>拥抱 (2013新录制作品)</t>
-  </si>
-  <si>
     <t>伤心的人别听慢歌(贯彻快乐)</t>
   </si>
   <si>
@@ -541,12 +541,6 @@
     <t>离开地球表面</t>
   </si>
   <si>
-    <t>知足 (乐团版)</t>
-  </si>
-  <si>
-    <t>温柔 (2013Remix版)</t>
-  </si>
-  <si>
     <t>你是唯一 (2013新录制作品)</t>
   </si>
   <si>
@@ -556,49 +550,22 @@
     <t>步步 自选作品辑</t>
   </si>
   <si>
-    <t>album_name</t>
-  </si>
-  <si>
     <t>song_name</t>
   </si>
   <si>
-    <t>爱情万岁 汇总</t>
-  </si>
-  <si>
-    <t>步步 自选作品辑 汇总</t>
-  </si>
-  <si>
-    <t>第二人生 (明日版) 汇总</t>
-  </si>
-  <si>
-    <t>第二人生 (末日版) 汇总</t>
-  </si>
-  <si>
-    <t>第一张创作专辑 汇总</t>
-  </si>
-  <si>
-    <t>后青春期的诗 汇总</t>
-  </si>
-  <si>
-    <t>人生海海 汇总</t>
-  </si>
-  <si>
-    <t>神的孩子都在跳舞 汇总</t>
-  </si>
-  <si>
-    <t>时光机 汇总</t>
-  </si>
-  <si>
-    <t>为爱而生 汇总</t>
-  </si>
-  <si>
-    <t>知足 最真杰作选 汇总</t>
-  </si>
-  <si>
-    <t>自传 汇总</t>
-  </si>
-  <si>
     <t>计数项:album_name</t>
+  </si>
+  <si>
+    <t>知足</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温柔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥抱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -658,7 +625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -675,6 +642,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -695,7 +665,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="m1" refreshedDate="46047.80786724537" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="190" xr:uid="{1B8A15CB-7EFB-864D-BBFD-435B64949287}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="m1" refreshedDate="46050.741616898151" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="190" xr:uid="{1B8A15CB-7EFB-864D-BBFD-435B64949287}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:K191" sheet="Sheet1"/>
   </cacheSource>
@@ -707,20 +677,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="38214" maxValue="34746073"/>
     </cacheField>
     <cacheField name="album_name" numFmtId="0">
-      <sharedItems count="12">
-        <s v="第一张创作专辑"/>
-        <s v="爱情万岁"/>
-        <s v="人生海海"/>
-        <s v="时光机"/>
-        <s v="神的孩子都在跳舞"/>
-        <s v="为爱而生"/>
-        <s v="后青春期的诗"/>
-        <s v="第二人生 (明日版)"/>
-        <s v="第二人生 (末日版)"/>
-        <s v="自传"/>
-        <s v="知足 最真杰作选"/>
-        <s v="步步 自选作品辑"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="album_type" numFmtId="0">
       <sharedItems/>
@@ -738,35 +695,35 @@
         <d v="2016-07-21T00:00:00"/>
         <d v="2005-08-26T00:00:00"/>
         <d v="2013-12-30T00:00:00"/>
-        <d v="2013-12-31T00:00:00"/>
-        <d v="2014-01-01T00:00:00"/>
-        <d v="2014-01-02T00:00:00"/>
-        <d v="2014-01-03T00:00:00"/>
-        <d v="2014-01-04T00:00:00"/>
-        <d v="2014-01-05T00:00:00"/>
-        <d v="2014-01-06T00:00:00"/>
-        <d v="2014-01-07T00:00:00"/>
-        <d v="2014-01-08T00:00:00"/>
-        <d v="2014-01-09T00:00:00"/>
-        <d v="2014-01-10T00:00:00"/>
-        <d v="2014-01-11T00:00:00"/>
-        <d v="2014-01-12T00:00:00"/>
-        <d v="2014-01-13T00:00:00"/>
-        <d v="2014-01-14T00:00:00"/>
-        <d v="2014-01-15T00:00:00"/>
-        <d v="2014-01-16T00:00:00"/>
-        <d v="2014-01-17T00:00:00"/>
-        <d v="2014-01-18T00:00:00"/>
-        <d v="2014-01-19T00:00:00"/>
-        <d v="2014-01-20T00:00:00"/>
-        <d v="2014-01-21T00:00:00"/>
-        <d v="2014-01-22T00:00:00"/>
-        <d v="2014-01-23T00:00:00"/>
-        <d v="2014-01-24T00:00:00"/>
-        <d v="2014-01-25T00:00:00"/>
-        <d v="2014-01-26T00:00:00"/>
-        <d v="2014-01-27T00:00:00"/>
-        <d v="2014-01-28T00:00:00"/>
+        <d v="2013-12-31T00:00:00" u="1"/>
+        <d v="2014-01-01T00:00:00" u="1"/>
+        <d v="2014-01-02T00:00:00" u="1"/>
+        <d v="2014-01-03T00:00:00" u="1"/>
+        <d v="2014-01-04T00:00:00" u="1"/>
+        <d v="2014-01-05T00:00:00" u="1"/>
+        <d v="2014-01-06T00:00:00" u="1"/>
+        <d v="2014-01-07T00:00:00" u="1"/>
+        <d v="2014-01-08T00:00:00" u="1"/>
+        <d v="2014-01-09T00:00:00" u="1"/>
+        <d v="2014-01-10T00:00:00" u="1"/>
+        <d v="2014-01-11T00:00:00" u="1"/>
+        <d v="2014-01-12T00:00:00" u="1"/>
+        <d v="2014-01-13T00:00:00" u="1"/>
+        <d v="2014-01-14T00:00:00" u="1"/>
+        <d v="2014-01-15T00:00:00" u="1"/>
+        <d v="2014-01-16T00:00:00" u="1"/>
+        <d v="2014-01-17T00:00:00" u="1"/>
+        <d v="2014-01-18T00:00:00" u="1"/>
+        <d v="2014-01-19T00:00:00" u="1"/>
+        <d v="2014-01-20T00:00:00" u="1"/>
+        <d v="2014-01-21T00:00:00" u="1"/>
+        <d v="2014-01-22T00:00:00" u="1"/>
+        <d v="2014-01-23T00:00:00" u="1"/>
+        <d v="2014-01-24T00:00:00" u="1"/>
+        <d v="2014-01-25T00:00:00" u="1"/>
+        <d v="2014-01-26T00:00:00" u="1"/>
+        <d v="2014-01-27T00:00:00" u="1"/>
+        <d v="2014-01-28T00:00:00" u="1"/>
       </sharedItems>
       <fieldGroup par="13"/>
     </cacheField>
@@ -776,8 +733,8 @@
     <cacheField name="song_id" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="385542" maxValue="2008204010"/>
     </cacheField>
-    <cacheField name="song_name" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2012" maxValue="2012" count="140">
+    <cacheField name="song_name" numFmtId="49">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2012" maxValue="2012" count="137">
         <s v="疯狂世界"/>
         <s v="拥抱"/>
         <s v="透露"/>
@@ -909,31 +866,16 @@
         <s v="未来 (Sailing With Me)"/>
         <s v="咸鱼"/>
         <s v="步步"/>
-        <s v="拥抱 (2013新录制作品)"/>
         <s v="伤心的人别听慢歌(贯彻快乐)"/>
         <s v="洋葱 (2013新录制作品)"/>
         <s v="入阵曲"/>
         <s v="离开地球表面"/>
-        <s v="知足 (乐团版)"/>
-        <s v="温柔 (2013Remix版)"/>
         <s v="你是唯一 (2013新录制作品)"/>
         <s v="盛夏光年"/>
       </sharedItems>
     </cacheField>
     <cacheField name="album_fixed" numFmtId="0">
-      <sharedItems count="11">
-        <s v="第一张创作专辑"/>
-        <s v="爱情万岁"/>
-        <s v="人生海海"/>
-        <s v="时光机"/>
-        <s v="神的孩子都在跳舞"/>
-        <s v="为爱而生"/>
-        <s v="后青春期的诗"/>
-        <s v="第二人生"/>
-        <s v="自传"/>
-        <s v="知足 最真杰作选"/>
-        <s v="步步 自选作品辑"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="has_lyric" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
@@ -1016,2470 +958,2470 @@
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="1"/>
     <n v="386925"/>
     <x v="0"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="2"/>
     <n v="386927"/>
     <x v="1"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="3"/>
     <n v="386929"/>
     <x v="2"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="4"/>
     <n v="386930"/>
     <x v="3"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="5"/>
     <n v="386931"/>
     <x v="4"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="6"/>
     <n v="386932"/>
     <x v="5"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="7"/>
     <n v="386934"/>
     <x v="6"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="8"/>
     <n v="386936"/>
     <x v="7"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="9"/>
     <n v="386939"/>
     <x v="8"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="10"/>
     <n v="386942"/>
     <x v="9"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="11"/>
     <n v="386948"/>
     <x v="10"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="1"/>
     <n v="38315"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <s v="录音室专辑"/>
     <x v="0"/>
     <n v="12"/>
     <n v="386951"/>
     <x v="11"/>
-    <x v="0"/>
+    <s v="第一张创作专辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="1"/>
     <n v="386839"/>
     <x v="12"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="2"/>
     <n v="386842"/>
     <x v="13"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="3"/>
     <n v="386846"/>
     <x v="14"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="4"/>
     <n v="386848"/>
     <x v="15"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="5"/>
     <n v="386851"/>
     <x v="16"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="6"/>
     <n v="386854"/>
     <x v="17"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="7"/>
     <n v="386857"/>
     <x v="18"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="8"/>
     <n v="386860"/>
     <x v="19"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="9"/>
     <n v="386863"/>
     <x v="20"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="10"/>
     <n v="386866"/>
     <x v="21"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="11"/>
     <n v="386870"/>
     <x v="22"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="2"/>
     <n v="38308"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <s v="录音室专辑"/>
     <x v="1"/>
     <n v="12"/>
     <n v="386874"/>
     <x v="23"/>
-    <x v="1"/>
+    <s v="爱情万岁"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="1"/>
     <n v="386691"/>
     <x v="24"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="2"/>
     <n v="386694"/>
     <x v="25"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="3"/>
     <n v="386697"/>
     <x v="26"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="4"/>
     <n v="386700"/>
     <x v="27"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="5"/>
     <n v="386702"/>
     <x v="28"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="6"/>
     <n v="386705"/>
     <x v="29"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="7"/>
     <n v="386709"/>
     <x v="30"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="8"/>
     <n v="386711"/>
     <x v="31"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="9"/>
     <n v="386713"/>
     <x v="32"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="10"/>
     <n v="386715"/>
     <x v="33"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="11"/>
     <n v="386716"/>
     <x v="34"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="3"/>
     <n v="38297"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <s v="录音室专辑"/>
     <x v="2"/>
     <n v="12"/>
     <n v="386717"/>
     <x v="35"/>
-    <x v="2"/>
+    <s v="人生海海"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="1"/>
     <n v="386443"/>
     <x v="36"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="2"/>
     <n v="386445"/>
     <x v="37"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="3"/>
     <n v="386447"/>
     <x v="38"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="4"/>
     <n v="386449"/>
     <x v="39"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="5"/>
     <n v="386451"/>
     <x v="40"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="6"/>
     <n v="386453"/>
     <x v="41"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="7"/>
     <n v="386457"/>
     <x v="42"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="8"/>
     <n v="386461"/>
     <x v="43"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="9"/>
     <n v="386465"/>
     <x v="44"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="10"/>
     <n v="386469"/>
     <x v="45"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="11"/>
     <n v="386473"/>
     <x v="46"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="12"/>
     <n v="386476"/>
     <x v="47"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="13"/>
     <n v="386479"/>
     <x v="48"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="14"/>
     <n v="386482"/>
     <x v="49"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="4"/>
     <n v="38276"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <s v="录音室专辑"/>
     <x v="3"/>
     <n v="15"/>
     <n v="386485"/>
     <x v="50"/>
-    <x v="3"/>
+    <s v="时光机"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="1"/>
     <n v="386173"/>
     <x v="51"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="2"/>
     <n v="386175"/>
     <x v="52"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="3"/>
     <n v="386177"/>
     <x v="53"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="4"/>
     <n v="386179"/>
     <x v="54"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="5"/>
     <n v="386181"/>
     <x v="55"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="6"/>
     <n v="386183"/>
     <x v="56"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="7"/>
     <n v="386185"/>
     <x v="57"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="8"/>
     <n v="386187"/>
     <x v="58"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="9"/>
     <n v="386189"/>
     <x v="59"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="10"/>
     <n v="386191"/>
     <x v="60"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="11"/>
     <n v="386193"/>
     <x v="61"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="0"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="12"/>
     <n v="386195"/>
     <x v="62"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="5"/>
     <n v="38259"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <s v="录音室专辑"/>
     <x v="4"/>
     <n v="13"/>
     <n v="386197"/>
     <x v="63"/>
-    <x v="4"/>
+    <s v="神的孩子都在跳舞"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="1"/>
     <n v="385884"/>
     <x v="64"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="0"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="2"/>
     <n v="385887"/>
     <x v="65"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="3"/>
     <n v="385891"/>
     <x v="66"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="4"/>
     <n v="385894"/>
     <x v="67"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="5"/>
     <n v="385897"/>
     <x v="68"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="6"/>
     <n v="385901"/>
     <x v="69"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="7"/>
     <n v="385905"/>
     <x v="70"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="8"/>
     <n v="385909"/>
     <x v="71"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="9"/>
     <n v="385913"/>
     <x v="72"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="10"/>
     <n v="385917"/>
     <x v="73"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="11"/>
     <n v="385921"/>
     <x v="74"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="12"/>
     <n v="385925"/>
     <x v="75"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="6"/>
     <n v="38241"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <s v="录音室专辑"/>
     <x v="5"/>
     <n v="13"/>
     <n v="385929"/>
     <x v="76"/>
-    <x v="5"/>
+    <s v="为爱而生"/>
     <n v="0"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="1"/>
     <n v="385781"/>
     <x v="77"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="2"/>
     <n v="385784"/>
     <x v="78"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="3"/>
     <n v="385787"/>
     <x v="79"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="4"/>
     <n v="385789"/>
     <x v="80"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="5"/>
     <n v="385791"/>
     <x v="81"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="6"/>
     <n v="385793"/>
     <x v="82"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="7"/>
     <n v="385795"/>
     <x v="83"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="8"/>
     <n v="385798"/>
     <x v="84"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="9"/>
     <n v="22198018"/>
     <x v="85"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="10"/>
     <n v="22198023"/>
     <x v="86"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="11"/>
     <n v="22198024"/>
     <x v="87"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="7"/>
     <n v="38235"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <s v="录音室专辑"/>
     <x v="6"/>
     <n v="12"/>
     <n v="22198025"/>
     <x v="88"/>
-    <x v="6"/>
+    <s v="后青春期的诗"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="1"/>
     <n v="22196001"/>
     <x v="89"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="2"/>
     <n v="22196002"/>
     <x v="90"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="3"/>
     <n v="22197001"/>
     <x v="91"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="4"/>
     <n v="22197003"/>
     <x v="92"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="5"/>
     <n v="22197004"/>
     <x v="93"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="6"/>
     <n v="22197005"/>
     <x v="94"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="7"/>
     <n v="22197007"/>
     <x v="95"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="8"/>
     <n v="22197008"/>
     <x v="96"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="9"/>
     <n v="22197009"/>
     <x v="97"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="10"/>
     <n v="22197010"/>
     <x v="98"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="11"/>
     <n v="22197011"/>
     <x v="99"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="12"/>
     <n v="22197012"/>
     <x v="100"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="0"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="13"/>
     <n v="22197014"/>
     <x v="101"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="2040001"/>
-    <x v="7"/>
+    <s v="第二人生 (明日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="14"/>
     <n v="2008204010"/>
     <x v="102"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="1"/>
     <n v="385542"/>
     <x v="97"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="2"/>
     <n v="385544"/>
     <x v="96"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="3"/>
     <n v="385547"/>
     <x v="92"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="4"/>
     <n v="385550"/>
     <x v="94"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="5"/>
     <n v="385552"/>
     <x v="95"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="6"/>
     <n v="385554"/>
     <x v="90"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="7"/>
     <n v="385556"/>
     <x v="91"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="8"/>
     <n v="385558"/>
     <x v="93"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="9"/>
     <n v="385561"/>
     <x v="103"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="0"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="10"/>
     <n v="385563"/>
     <x v="104"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="11"/>
     <n v="385565"/>
     <x v="98"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="12"/>
     <n v="385566"/>
     <x v="99"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="13"/>
     <n v="385568"/>
     <x v="89"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="8"/>
     <n v="38214"/>
-    <x v="8"/>
+    <s v="第二人生 (末日版)"/>
     <s v="录音室专辑"/>
     <x v="7"/>
     <n v="14"/>
     <n v="385576"/>
     <x v="102"/>
-    <x v="7"/>
+    <s v="第二人生"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="1"/>
     <n v="417953659"/>
     <x v="105"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="2"/>
     <n v="422094252"/>
     <x v="106"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="3"/>
     <n v="422094253"/>
     <x v="107"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="4"/>
     <n v="422094254"/>
     <x v="108"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="5"/>
     <n v="422104164"/>
     <x v="109"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="6"/>
     <n v="422104138"/>
     <x v="110"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="7"/>
     <n v="422104166"/>
     <x v="111"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="8"/>
     <n v="417953658"/>
     <x v="112"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="9"/>
     <n v="422104165"/>
     <x v="113"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="10"/>
     <n v="422094255"/>
     <x v="114"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="11"/>
     <n v="422104167"/>
     <x v="115"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="12"/>
     <n v="422094256"/>
     <x v="116"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="9"/>
     <n v="34746073"/>
-    <x v="9"/>
+    <s v="自传"/>
     <s v="录音室专辑"/>
     <x v="8"/>
     <n v="13"/>
     <n v="422094257"/>
     <x v="117"/>
-    <x v="8"/>
+    <s v="自传"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="1"/>
     <n v="385965"/>
     <x v="118"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="2"/>
     <n v="385967"/>
     <x v="119"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="3"/>
     <n v="385970"/>
     <x v="120"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="4"/>
     <n v="385973"/>
     <x v="121"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="5"/>
     <n v="385976"/>
     <x v="122"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="6"/>
     <n v="386021"/>
     <x v="17"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="7"/>
     <n v="385979"/>
     <x v="1"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="8"/>
     <n v="385981"/>
     <x v="13"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="9"/>
     <n v="385984"/>
     <x v="40"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="10"/>
     <n v="385987"/>
     <x v="51"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="11"/>
     <n v="385990"/>
     <x v="35"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="12"/>
     <n v="386032"/>
     <x v="6"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="13"/>
     <n v="385993"/>
     <x v="0"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="14"/>
     <n v="386034"/>
     <x v="10"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="15"/>
     <n v="385996"/>
     <x v="22"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="16"/>
     <n v="385999"/>
     <x v="37"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="17"/>
     <n v="386001"/>
     <x v="123"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="18"/>
     <n v="386005"/>
     <x v="52"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="19"/>
     <n v="386007"/>
     <x v="124"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="20"/>
     <n v="386010"/>
     <x v="125"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="21"/>
     <n v="386011"/>
     <x v="7"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="22"/>
     <n v="386014"/>
     <x v="15"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="23"/>
     <n v="386017"/>
     <x v="26"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="24"/>
     <n v="386025"/>
     <x v="126"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="25"/>
     <n v="386028"/>
     <x v="127"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="26"/>
     <n v="386030"/>
     <x v="18"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="27"/>
     <n v="386035"/>
     <x v="30"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="28"/>
     <n v="386036"/>
     <x v="29"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="29"/>
     <n v="386038"/>
     <x v="128"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="0"/>
     <n v="0"/>
   </r>
   <r>
     <n v="10"/>
     <n v="38247"/>
-    <x v="10"/>
+    <s v="知足 最真杰作选"/>
     <s v="精选辑"/>
     <x v="9"/>
     <n v="30"/>
     <n v="386040"/>
     <x v="129"/>
-    <x v="9"/>
+    <s v="知足 最真杰作选"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
     <x v="10"/>
     <n v="1"/>
     <n v="28181103"/>
     <x v="130"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="11"/>
+    <x v="10"/>
     <n v="2"/>
     <n v="28181105"/>
-    <x v="131"/>
-    <x v="10"/>
-    <n v="1"/>
-    <n v="0"/>
+    <x v="1"/>
+    <s v="步步 自选作品辑"/>
+    <n v="1"/>
+    <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="12"/>
+    <x v="10"/>
     <n v="3"/>
     <n v="28181107"/>
-    <x v="132"/>
-    <x v="10"/>
+    <x v="131"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="13"/>
+    <x v="10"/>
     <n v="4"/>
     <n v="28181109"/>
-    <x v="133"/>
-    <x v="10"/>
+    <x v="132"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="14"/>
+    <x v="10"/>
     <n v="5"/>
     <n v="28181111"/>
     <x v="95"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="15"/>
+    <x v="10"/>
     <n v="6"/>
     <n v="28181113"/>
-    <x v="134"/>
-    <x v="10"/>
+    <x v="133"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="16"/>
+    <x v="10"/>
     <n v="7"/>
     <n v="28181115"/>
     <x v="52"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="17"/>
+    <x v="10"/>
     <n v="8"/>
     <n v="28181117"/>
     <x v="77"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="18"/>
+    <x v="10"/>
     <n v="9"/>
     <n v="28181119"/>
     <x v="121"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="19"/>
+    <x v="10"/>
     <n v="10"/>
     <n v="28181121"/>
-    <x v="135"/>
-    <x v="10"/>
+    <x v="134"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="20"/>
+    <x v="10"/>
     <n v="11"/>
     <n v="28181123"/>
     <x v="91"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="21"/>
+    <x v="10"/>
     <n v="12"/>
     <n v="28181125"/>
     <x v="90"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="22"/>
+    <x v="10"/>
     <n v="13"/>
     <n v="28181127"/>
     <x v="35"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="23"/>
+    <x v="10"/>
     <n v="14"/>
     <n v="28181129"/>
-    <x v="136"/>
-    <x v="10"/>
-    <n v="1"/>
-    <n v="0"/>
+    <x v="118"/>
+    <s v="步步 自选作品辑"/>
+    <n v="1"/>
+    <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="24"/>
+    <x v="10"/>
     <n v="15"/>
     <n v="28181131"/>
-    <x v="137"/>
-    <x v="10"/>
-    <n v="1"/>
-    <n v="0"/>
+    <x v="21"/>
+    <s v="步步 自选作品辑"/>
+    <n v="1"/>
+    <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="25"/>
+    <x v="10"/>
     <n v="16"/>
     <n v="28181104"/>
-    <x v="138"/>
-    <x v="10"/>
+    <x v="135"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="26"/>
+    <x v="10"/>
     <n v="17"/>
     <n v="28181106"/>
     <x v="85"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="27"/>
+    <x v="10"/>
     <n v="18"/>
     <n v="28181108"/>
     <x v="86"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="28"/>
+    <x v="10"/>
     <n v="19"/>
     <n v="28181110"/>
-    <x v="139"/>
-    <x v="10"/>
+    <x v="136"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="0"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="29"/>
+    <x v="10"/>
     <n v="20"/>
     <n v="28181112"/>
     <x v="24"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="30"/>
+    <x v="10"/>
     <n v="21"/>
     <n v="28181114"/>
     <x v="93"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="31"/>
+    <x v="10"/>
     <n v="22"/>
     <n v="28181116"/>
     <x v="51"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="32"/>
+    <x v="10"/>
     <n v="23"/>
     <n v="28181118"/>
     <x v="69"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="33"/>
+    <x v="10"/>
     <n v="24"/>
     <n v="28181120"/>
     <x v="70"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="34"/>
+    <x v="10"/>
     <n v="25"/>
     <n v="28181122"/>
     <x v="22"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="35"/>
+    <x v="10"/>
     <n v="26"/>
     <n v="28181124"/>
     <x v="38"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="36"/>
+    <x v="10"/>
     <n v="27"/>
     <n v="28181126"/>
     <x v="48"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="37"/>
+    <x v="10"/>
     <n v="28"/>
     <n v="28181128"/>
     <x v="99"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="38"/>
+    <x v="10"/>
     <n v="29"/>
     <n v="28181130"/>
     <x v="83"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
   <r>
     <n v="11"/>
     <n v="2740205"/>
-    <x v="11"/>
+    <s v="步步 自选作品辑"/>
     <s v="精选辑"/>
-    <x v="39"/>
+    <x v="10"/>
     <n v="30"/>
     <n v="28181132"/>
     <x v="17"/>
-    <x v="10"/>
+    <s v="步步 自选作品辑"/>
     <n v="1"/>
     <n v="1"/>
   </r>
@@ -3487,28 +3429,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F53B5E73-1E1B-C048-9495-86A00DE5D8A9}" name="数据透视表1" cacheId="52" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A3:C206" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F53B5E73-1E1B-C048-9495-86A00DE5D8A9}" name="数据透视表1" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:B141" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0">
-      <items count="13">
-        <item x="1"/>
-        <item x="11"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" numFmtId="14" outline="0" subtotalTop="0" showAll="0">
       <items count="41">
@@ -3523,42 +3449,42 @@
         <item x="7"/>
         <item x="8"/>
         <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
+        <item m="1" x="11"/>
+        <item m="1" x="12"/>
+        <item m="1" x="13"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
+        <item m="1" x="16"/>
+        <item m="1" x="17"/>
+        <item m="1" x="18"/>
+        <item m="1" x="19"/>
+        <item m="1" x="20"/>
+        <item m="1" x="21"/>
+        <item m="1" x="22"/>
+        <item m="1" x="23"/>
+        <item m="1" x="24"/>
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="27"/>
+        <item m="1" x="28"/>
+        <item m="1" x="29"/>
+        <item m="1" x="30"/>
+        <item m="1" x="31"/>
+        <item m="1" x="32"/>
+        <item m="1" x="33"/>
+        <item m="1" x="34"/>
+        <item m="1" x="35"/>
+        <item m="1" x="36"/>
+        <item m="1" x="37"/>
+        <item m="1" x="38"/>
+        <item m="1" x="39"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
-      <items count="141">
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" sortType="descending">
+      <items count="138">
         <item x="97"/>
         <item x="8"/>
         <item x="10"/>
@@ -3610,7 +3536,7 @@
         <item x="53"/>
         <item x="127"/>
         <item x="63"/>
-        <item x="135"/>
+        <item x="134"/>
         <item x="121"/>
         <item x="120"/>
         <item x="20"/>
@@ -3622,7 +3548,7 @@
         <item x="103"/>
         <item x="25"/>
         <item x="79"/>
-        <item x="138"/>
+        <item x="135"/>
         <item x="99"/>
         <item x="81"/>
         <item x="112"/>
@@ -3634,16 +3560,16 @@
         <item x="116"/>
         <item x="105"/>
         <item x="86"/>
-        <item x="134"/>
+        <item x="133"/>
         <item x="93"/>
-        <item x="132"/>
+        <item x="131"/>
         <item x="114"/>
         <item x="61"/>
         <item x="78"/>
         <item x="3"/>
         <item x="48"/>
         <item x="62"/>
-        <item x="139"/>
+        <item x="136"/>
         <item x="45"/>
         <item x="51"/>
         <item x="76"/>
@@ -3660,7 +3586,6 @@
         <item x="12"/>
         <item x="128"/>
         <item x="21"/>
-        <item x="137"/>
         <item x="123"/>
         <item x="90"/>
         <item x="46"/>
@@ -3678,12 +3603,11 @@
         <item x="91"/>
         <item x="108"/>
         <item x="119"/>
-        <item x="133"/>
+        <item x="132"/>
         <item x="85"/>
         <item x="24"/>
         <item x="75"/>
         <item x="1"/>
-        <item x="131"/>
         <item x="30"/>
         <item x="16"/>
         <item x="89"/>
@@ -3692,7 +3616,6 @@
         <item x="47"/>
         <item x="6"/>
         <item x="118"/>
-        <item x="136"/>
         <item x="7"/>
         <item x="13"/>
         <item x="115"/>
@@ -3701,23 +3624,17 @@
         <item x="70"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0">
-      <items count="12">
-        <item x="1"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0">
@@ -3776,628 +3693,420 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="2">
-    <field x="2"/>
+  <rowFields count="1">
     <field x="7"/>
   </rowFields>
-  <rowItems count="203">
+  <rowItems count="138">
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="115"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="120"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="129"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="123"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="131"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
     <i>
       <x/>
-      <x v="10"/>
-    </i>
-    <i r="1">
+    </i>
+    <i>
+      <x v="114"/>
+    </i>
+    <i>
+      <x v="132"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="125"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="130"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="136"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="113"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="117"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="133"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="127"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="135"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
       <x v="27"/>
     </i>
-    <i r="1">
-      <x v="31"/>
-    </i>
-    <i r="1">
-      <x v="41"/>
-    </i>
-    <i r="1">
-      <x v="54"/>
-    </i>
-    <i r="1">
-      <x v="57"/>
-    </i>
-    <i r="1">
-      <x v="98"/>
-    </i>
-    <i r="1">
-      <x v="100"/>
-    </i>
-    <i r="1">
-      <x v="115"/>
-    </i>
-    <i r="1">
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="106"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="116"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="118"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="124"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
       <x v="126"/>
     </i>
-    <i r="1">
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
       <x v="128"/>
     </i>
-    <i r="1">
-      <x v="135"/>
-    </i>
-    <i t="default">
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x v="10"/>
-    </i>
-    <i r="1">
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
       <x v="13"/>
     </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i r="1">
-      <x v="30"/>
-    </i>
-    <i r="1">
-      <x v="31"/>
-    </i>
-    <i r="1">
-      <x v="46"/>
-    </i>
-    <i r="1">
-      <x v="51"/>
-    </i>
-    <i r="1">
-      <x v="52"/>
-    </i>
-    <i r="1">
-      <x v="59"/>
-    </i>
-    <i r="1">
-      <x v="63"/>
-    </i>
-    <i r="1">
-      <x v="64"/>
-    </i>
-    <i r="1">
-      <x v="70"/>
-    </i>
-    <i r="1">
-      <x v="74"/>
-    </i>
-    <i r="1">
-      <x v="75"/>
-    </i>
-    <i r="1">
-      <x v="76"/>
-    </i>
-    <i r="1">
-      <x v="77"/>
-    </i>
-    <i r="1">
-      <x v="82"/>
-    </i>
-    <i r="1">
-      <x v="84"/>
-    </i>
-    <i r="1">
-      <x v="86"/>
-    </i>
-    <i r="1">
-      <x v="91"/>
-    </i>
-    <i r="1">
-      <x v="101"/>
-    </i>
-    <i r="1">
-      <x v="103"/>
-    </i>
-    <i r="1">
-      <x v="105"/>
-    </i>
-    <i r="1">
-      <x v="116"/>
-    </i>
-    <i r="1">
-      <x v="119"/>
-    </i>
-    <i r="1">
-      <x v="120"/>
-    </i>
-    <i r="1">
-      <x v="121"/>
-    </i>
-    <i r="1">
-      <x v="124"/>
-    </i>
-    <i r="1">
-      <x v="133"/>
-    </i>
-    <i r="1">
-      <x v="139"/>
-    </i>
-    <i t="default">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-    </i>
-    <i r="1">
-      <x v="30"/>
-    </i>
-    <i r="1">
-      <x v="58"/>
-    </i>
-    <i r="1">
-      <x v="64"/>
-    </i>
-    <i r="1">
-      <x v="76"/>
-    </i>
-    <i r="1">
-      <x v="92"/>
-    </i>
-    <i r="1">
-      <x v="103"/>
-    </i>
-    <i r="1">
-      <x v="108"/>
-    </i>
-    <i r="1">
-      <x v="116"/>
-    </i>
-    <i r="1">
-      <x v="127"/>
-    </i>
-    <i t="default">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-    </i>
-    <i r="1">
-      <x v="30"/>
-    </i>
-    <i r="1">
-      <x v="60"/>
-    </i>
-    <i r="1">
-      <x v="64"/>
-    </i>
-    <i r="1">
-      <x v="76"/>
-    </i>
-    <i r="1">
-      <x v="92"/>
-    </i>
-    <i r="1">
-      <x v="103"/>
-    </i>
-    <i r="1">
-      <x v="108"/>
-    </i>
-    <i r="1">
-      <x v="116"/>
-    </i>
-    <i r="1">
-      <x v="127"/>
-    </i>
-    <i t="default">
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="28"/>
-    </i>
-    <i r="1">
-      <x v="29"/>
-    </i>
-    <i r="1">
-      <x v="34"/>
-    </i>
-    <i r="1">
-      <x v="35"/>
-    </i>
-    <i r="1">
-      <x v="81"/>
-    </i>
-    <i r="1">
-      <x v="90"/>
-    </i>
-    <i r="1">
-      <x v="123"/>
-    </i>
-    <i r="1">
-      <x v="131"/>
-    </i>
-    <i r="1">
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
       <x v="134"/>
     </i>
-    <i t="default">
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="19"/>
-    </i>
-    <i r="1">
-      <x v="20"/>
-    </i>
-    <i r="1">
-      <x v="38"/>
-    </i>
-    <i r="1">
-      <x v="62"/>
-    </i>
-    <i r="1">
-      <x v="65"/>
-    </i>
-    <i r="1">
-      <x v="74"/>
-    </i>
-    <i r="1">
-      <x v="80"/>
-    </i>
-    <i r="1">
-      <x v="91"/>
-    </i>
-    <i r="1">
-      <x v="105"/>
-    </i>
-    <i r="1">
-      <x v="114"/>
-    </i>
-    <i r="1">
-      <x v="120"/>
-    </i>
-    <i t="default">
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="14"/>
-    </i>
-    <i r="1">
-      <x v="21"/>
-    </i>
-    <i r="1">
-      <x v="32"/>
-    </i>
-    <i r="1">
-      <x v="39"/>
-    </i>
-    <i r="1">
-      <x v="42"/>
-    </i>
-    <i r="1">
-      <x v="44"/>
-    </i>
-    <i r="1">
-      <x v="61"/>
-    </i>
-    <i r="1">
-      <x v="70"/>
-    </i>
-    <i r="1">
-      <x v="110"/>
-    </i>
-    <i r="1">
-      <x v="121"/>
-    </i>
-    <i r="1">
-      <x v="125"/>
-    </i>
-    <i t="default">
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-      <x v="16"/>
-    </i>
-    <i r="1">
-      <x v="23"/>
-    </i>
-    <i r="1">
-      <x v="40"/>
-    </i>
-    <i r="1">
-      <x v="46"/>
-    </i>
-    <i r="1">
-      <x v="48"/>
-    </i>
-    <i r="1">
-      <x v="50"/>
-    </i>
-    <i r="1">
-      <x v="69"/>
-    </i>
-    <i r="1">
-      <x v="79"/>
-    </i>
-    <i r="1">
-      <x v="83"/>
-    </i>
-    <i r="1">
-      <x v="86"/>
-    </i>
-    <i r="1">
-      <x v="94"/>
-    </i>
-    <i r="1">
-      <x v="112"/>
-    </i>
-    <i r="1">
-      <x v="129"/>
-    </i>
-    <i t="default">
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i r="1">
-      <x v="25"/>
-    </i>
-    <i r="1">
-      <x v="26"/>
-    </i>
-    <i r="1">
-      <x v="36"/>
-    </i>
-    <i r="1">
-      <x v="45"/>
-    </i>
-    <i r="1">
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
       <x v="68"/>
-    </i>
-    <i r="1">
-      <x v="82"/>
-    </i>
-    <i r="1">
-      <x v="85"/>
-    </i>
-    <i r="1">
-      <x v="95"/>
-    </i>
-    <i r="1">
-      <x v="104"/>
-    </i>
-    <i r="1">
-      <x v="107"/>
-    </i>
-    <i r="1">
-      <x v="113"/>
-    </i>
-    <i r="1">
-      <x v="130"/>
-    </i>
-    <i t="default">
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="47"/>
-    </i>
-    <i r="1">
-      <x v="56"/>
-    </i>
-    <i r="1">
-      <x v="59"/>
-    </i>
-    <i r="1">
-      <x v="67"/>
-    </i>
-    <i r="1">
-      <x v="87"/>
-    </i>
-    <i r="1">
-      <x v="88"/>
-    </i>
-    <i r="1">
-      <x v="96"/>
-    </i>
-    <i r="1">
-      <x v="97"/>
-    </i>
-    <i r="1">
-      <x v="106"/>
-    </i>
-    <i r="1">
-      <x v="111"/>
-    </i>
-    <i r="1">
-      <x v="122"/>
-    </i>
-    <i r="1">
-      <x v="139"/>
-    </i>
-    <i t="default">
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="26"/>
-    </i>
-    <i r="1">
-      <x v="29"/>
-    </i>
-    <i r="1">
-      <x v="31"/>
-    </i>
-    <i r="1">
-      <x v="32"/>
-    </i>
-    <i r="1">
-      <x v="36"/>
-    </i>
-    <i r="1">
-      <x v="41"/>
-    </i>
-    <i r="1">
-      <x v="42"/>
-    </i>
-    <i r="1">
-      <x v="43"/>
-    </i>
-    <i r="1">
-      <x v="46"/>
-    </i>
-    <i r="1">
-      <x v="49"/>
-    </i>
-    <i r="1">
-      <x v="52"/>
-    </i>
-    <i r="1">
-      <x v="53"/>
-    </i>
-    <i r="1">
-      <x v="55"/>
-    </i>
-    <i r="1">
-      <x v="70"/>
-    </i>
-    <i r="1">
-      <x v="86"/>
-    </i>
-    <i r="1">
-      <x v="89"/>
-    </i>
-    <i r="1">
-      <x v="99"/>
-    </i>
-    <i r="1">
-      <x v="102"/>
-    </i>
-    <i r="1">
-      <x v="109"/>
-    </i>
-    <i r="1">
-      <x v="115"/>
-    </i>
-    <i r="1">
-      <x v="118"/>
-    </i>
-    <i r="1">
-      <x v="123"/>
-    </i>
-    <i r="1">
-      <x v="125"/>
-    </i>
-    <i r="1">
-      <x v="131"/>
-    </i>
-    <i r="1">
-      <x v="132"/>
-    </i>
-    <i r="1">
-      <x v="134"/>
-    </i>
-    <i r="1">
-      <x v="135"/>
-    </i>
-    <i t="default">
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="33"/>
-    </i>
-    <i r="1">
-      <x v="37"/>
-    </i>
-    <i r="1">
-      <x v="66"/>
-    </i>
-    <i r="1">
-      <x v="71"/>
-    </i>
-    <i r="1">
-      <x v="72"/>
-    </i>
-    <i r="1">
-      <x v="73"/>
-    </i>
-    <i r="1">
-      <x v="78"/>
-    </i>
-    <i r="1">
-      <x v="93"/>
-    </i>
-    <i r="1">
-      <x v="117"/>
-    </i>
-    <i r="1">
-      <x v="136"/>
-    </i>
-    <i r="1">
-      <x v="137"/>
-    </i>
-    <i r="1">
-      <x v="138"/>
-    </i>
-    <i t="default">
-      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
@@ -4745,7 +4454,7 @@
     <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4771,7 +4480,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" t="s">
@@ -4806,7 +4515,7 @@
       <c r="G2">
         <v>386925</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -4841,7 +4550,7 @@
       <c r="G3">
         <v>386927</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -4876,7 +4585,7 @@
       <c r="G4">
         <v>386929</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -4911,7 +4620,7 @@
       <c r="G5">
         <v>386930</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -4946,7 +4655,7 @@
       <c r="G6">
         <v>386931</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -4981,7 +4690,7 @@
       <c r="G7">
         <v>386932</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -5016,7 +4725,7 @@
       <c r="G8">
         <v>386934</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -5051,7 +4760,7 @@
       <c r="G9">
         <v>386936</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -5086,7 +4795,7 @@
       <c r="G10">
         <v>386939</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -5121,7 +4830,7 @@
       <c r="G11">
         <v>386942</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -5156,7 +4865,7 @@
       <c r="G12">
         <v>386948</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -5191,7 +4900,7 @@
       <c r="G13">
         <v>386951</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="3" t="s">
@@ -5226,7 +4935,7 @@
       <c r="G14">
         <v>386839</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -5261,7 +4970,7 @@
       <c r="G15">
         <v>386842</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="6" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="3" t="s">
@@ -5296,7 +5005,7 @@
       <c r="G16">
         <v>386846</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -5331,7 +5040,7 @@
       <c r="G17">
         <v>386848</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
@@ -5366,7 +5075,7 @@
       <c r="G18">
         <v>386851</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -5401,7 +5110,7 @@
       <c r="G19">
         <v>386854</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I19" s="3" t="s">
@@ -5436,7 +5145,7 @@
       <c r="G20">
         <v>386857</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -5471,7 +5180,7 @@
       <c r="G21">
         <v>386860</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="3" t="s">
@@ -5506,7 +5215,7 @@
       <c r="G22">
         <v>386863</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="I22" s="3" t="s">
@@ -5541,7 +5250,7 @@
       <c r="G23">
         <v>386866</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="6" t="s">
         <v>29</v>
       </c>
       <c r="I23" s="3" t="s">
@@ -5576,7 +5285,7 @@
       <c r="G24">
         <v>386870</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
@@ -5611,7 +5320,7 @@
       <c r="G25">
         <v>386874</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
@@ -5646,7 +5355,7 @@
       <c r="G26">
         <v>386691</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -5681,7 +5390,7 @@
       <c r="G27">
         <v>386694</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="6" t="s">
         <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
@@ -5716,7 +5425,7 @@
       <c r="G28">
         <v>386697</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="6" t="s">
         <v>34</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -5751,7 +5460,7 @@
       <c r="G29">
         <v>386700</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="6" t="s">
         <v>35</v>
       </c>
       <c r="I29" s="3" t="s">
@@ -5786,7 +5495,7 @@
       <c r="G30">
         <v>386702</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="6" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -5821,7 +5530,7 @@
       <c r="G31">
         <v>386705</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -5856,7 +5565,7 @@
       <c r="G32">
         <v>386709</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="6" t="s">
         <v>38</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -5891,7 +5600,7 @@
       <c r="G33">
         <v>386711</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I33" s="3" t="s">
@@ -5926,7 +5635,7 @@
       <c r="G34">
         <v>386713</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="6" t="s">
         <v>40</v>
       </c>
       <c r="I34" s="3" t="s">
@@ -5961,7 +5670,7 @@
       <c r="G35">
         <v>386715</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="6" t="s">
         <v>41</v>
       </c>
       <c r="I35" s="3" t="s">
@@ -5996,7 +5705,7 @@
       <c r="G36">
         <v>386716</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="6" t="s">
         <v>42</v>
       </c>
       <c r="I36" s="3" t="s">
@@ -6031,7 +5740,7 @@
       <c r="G37">
         <v>386717</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I37" s="3" t="s">
@@ -6066,7 +5775,7 @@
       <c r="G38">
         <v>386443</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I38" s="3" t="s">
@@ -6101,7 +5810,7 @@
       <c r="G39">
         <v>386445</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I39" s="3" t="s">
@@ -6136,7 +5845,7 @@
       <c r="G40">
         <v>386447</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="6" t="s">
         <v>47</v>
       </c>
       <c r="I40" s="3" t="s">
@@ -6171,7 +5880,7 @@
       <c r="G41">
         <v>386449</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="6" t="s">
         <v>48</v>
       </c>
       <c r="I41" s="3" t="s">
@@ -6206,7 +5915,7 @@
       <c r="G42">
         <v>386451</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -6241,7 +5950,7 @@
       <c r="G43">
         <v>386453</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I43" s="3" t="s">
@@ -6276,7 +5985,7 @@
       <c r="G44">
         <v>386457</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I44" s="3" t="s">
@@ -6311,7 +6020,7 @@
       <c r="G45">
         <v>386461</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="6" t="s">
         <v>52</v>
       </c>
       <c r="I45" s="3" t="s">
@@ -6346,7 +6055,7 @@
       <c r="G46">
         <v>386465</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I46" s="3" t="s">
@@ -6381,7 +6090,7 @@
       <c r="G47">
         <v>386469</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="6" t="s">
         <v>54</v>
       </c>
       <c r="I47" s="3" t="s">
@@ -6416,7 +6125,7 @@
       <c r="G48">
         <v>386473</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="6" t="s">
         <v>55</v>
       </c>
       <c r="I48" s="3" t="s">
@@ -6451,7 +6160,7 @@
       <c r="G49">
         <v>386476</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="6" t="s">
         <v>56</v>
       </c>
       <c r="I49" s="3" t="s">
@@ -6486,7 +6195,7 @@
       <c r="G50">
         <v>386479</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I50" s="3" t="s">
@@ -6521,7 +6230,7 @@
       <c r="G51">
         <v>386482</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="6" t="s">
         <v>58</v>
       </c>
       <c r="I51" s="3" t="s">
@@ -6556,7 +6265,7 @@
       <c r="G52">
         <v>386485</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I52" s="3" t="s">
@@ -6591,7 +6300,7 @@
       <c r="G53">
         <v>386173</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="6" t="s">
         <v>61</v>
       </c>
       <c r="I53" s="3" t="s">
@@ -6626,7 +6335,7 @@
       <c r="G54">
         <v>386175</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="6" t="s">
         <v>62</v>
       </c>
       <c r="I54" s="3" t="s">
@@ -6661,7 +6370,7 @@
       <c r="G55">
         <v>386177</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="6" t="s">
         <v>63</v>
       </c>
       <c r="I55" s="3" t="s">
@@ -6696,7 +6405,7 @@
       <c r="G56">
         <v>386179</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I56" s="3" t="s">
@@ -6731,7 +6440,7 @@
       <c r="G57">
         <v>386181</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="6" t="s">
         <v>65</v>
       </c>
       <c r="I57" s="3" t="s">
@@ -6766,7 +6475,7 @@
       <c r="G58">
         <v>386183</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I58" s="3" t="s">
@@ -6801,7 +6510,7 @@
       <c r="G59">
         <v>386185</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="6" t="s">
         <v>67</v>
       </c>
       <c r="I59" s="3" t="s">
@@ -6836,7 +6545,7 @@
       <c r="G60">
         <v>386187</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="6" t="s">
         <v>68</v>
       </c>
       <c r="I60" s="3" t="s">
@@ -6871,7 +6580,7 @@
       <c r="G61">
         <v>386189</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="6" t="s">
         <v>69</v>
       </c>
       <c r="I61" s="3" t="s">
@@ -6906,7 +6615,7 @@
       <c r="G62">
         <v>386191</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="6" t="s">
         <v>70</v>
       </c>
       <c r="I62" s="3" t="s">
@@ -6941,7 +6650,7 @@
       <c r="G63">
         <v>386193</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="6" t="s">
         <v>71</v>
       </c>
       <c r="I63" s="3" t="s">
@@ -6976,7 +6685,7 @@
       <c r="G64">
         <v>386195</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="6" t="s">
         <v>72</v>
       </c>
       <c r="I64" s="3" t="s">
@@ -7011,7 +6720,7 @@
       <c r="G65">
         <v>386197</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="6" t="s">
         <v>73</v>
       </c>
       <c r="I65" s="3" t="s">
@@ -7046,7 +6755,7 @@
       <c r="G66">
         <v>385884</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="6" t="s">
         <v>76</v>
       </c>
       <c r="I66" s="3" t="s">
@@ -7081,7 +6790,7 @@
       <c r="G67">
         <v>385887</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="6" t="s">
         <v>77</v>
       </c>
       <c r="I67" s="3" t="s">
@@ -7116,7 +6825,7 @@
       <c r="G68">
         <v>385891</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="6" t="s">
         <v>78</v>
       </c>
       <c r="I68" s="3" t="s">
@@ -7151,7 +6860,7 @@
       <c r="G69">
         <v>385894</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="6" t="s">
         <v>79</v>
       </c>
       <c r="I69" s="3" t="s">
@@ -7186,7 +6895,7 @@
       <c r="G70">
         <v>385897</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="6" t="s">
         <v>80</v>
       </c>
       <c r="I70" s="3" t="s">
@@ -7221,7 +6930,7 @@
       <c r="G71">
         <v>385901</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I71" s="3" t="s">
@@ -7256,7 +6965,7 @@
       <c r="G72">
         <v>385905</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H72" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I72" s="3" t="s">
@@ -7291,7 +7000,7 @@
       <c r="G73">
         <v>385909</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="6" t="s">
         <v>83</v>
       </c>
       <c r="I73" s="3" t="s">
@@ -7326,7 +7035,7 @@
       <c r="G74">
         <v>385913</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="6" t="s">
         <v>84</v>
       </c>
       <c r="I74" s="3" t="s">
@@ -7361,7 +7070,7 @@
       <c r="G75">
         <v>385917</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" s="6" t="s">
         <v>85</v>
       </c>
       <c r="I75" s="3" t="s">
@@ -7396,7 +7105,7 @@
       <c r="G76">
         <v>385921</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H76" s="6" t="s">
         <v>86</v>
       </c>
       <c r="I76" s="3" t="s">
@@ -7431,7 +7140,7 @@
       <c r="G77">
         <v>385925</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="6" t="s">
         <v>87</v>
       </c>
       <c r="I77" s="3" t="s">
@@ -7466,7 +7175,7 @@
       <c r="G78">
         <v>385929</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="6" t="s">
         <v>88</v>
       </c>
       <c r="I78" s="3" t="s">
@@ -7501,7 +7210,7 @@
       <c r="G79">
         <v>385781</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="6" t="s">
         <v>90</v>
       </c>
       <c r="I79" s="3" t="s">
@@ -7536,7 +7245,7 @@
       <c r="G80">
         <v>385784</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="6" t="s">
         <v>91</v>
       </c>
       <c r="I80" s="3" t="s">
@@ -7571,7 +7280,7 @@
       <c r="G81">
         <v>385787</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="6" t="s">
         <v>92</v>
       </c>
       <c r="I81" s="3" t="s">
@@ -7606,7 +7315,7 @@
       <c r="G82">
         <v>385789</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="6" t="s">
         <v>93</v>
       </c>
       <c r="I82" s="3" t="s">
@@ -7641,7 +7350,7 @@
       <c r="G83">
         <v>385791</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="6" t="s">
         <v>94</v>
       </c>
       <c r="I83" s="3" t="s">
@@ -7676,7 +7385,7 @@
       <c r="G84">
         <v>385793</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="6" t="s">
         <v>95</v>
       </c>
       <c r="I84" s="3" t="s">
@@ -7711,7 +7420,7 @@
       <c r="G85">
         <v>385795</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="6" t="s">
         <v>96</v>
       </c>
       <c r="I85" s="3" t="s">
@@ -7746,7 +7455,7 @@
       <c r="G86">
         <v>385798</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="6" t="s">
         <v>97</v>
       </c>
       <c r="I86" s="3" t="s">
@@ -7781,7 +7490,7 @@
       <c r="G87">
         <v>22198018</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="6" t="s">
         <v>98</v>
       </c>
       <c r="I87" s="3" t="s">
@@ -7816,7 +7525,7 @@
       <c r="G88">
         <v>22198023</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="6" t="s">
         <v>99</v>
       </c>
       <c r="I88" s="3" t="s">
@@ -7851,7 +7560,7 @@
       <c r="G89">
         <v>22198024</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="6" t="s">
         <v>100</v>
       </c>
       <c r="I89" s="3" t="s">
@@ -7886,7 +7595,7 @@
       <c r="G90">
         <v>22198025</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="6" t="s">
         <v>101</v>
       </c>
       <c r="I90" s="3" t="s">
@@ -7921,7 +7630,7 @@
       <c r="G91">
         <v>22196001</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="6" t="s">
         <v>103</v>
       </c>
       <c r="I91" s="3" t="s">
@@ -7956,7 +7665,7 @@
       <c r="G92">
         <v>22196002</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="6" t="s">
         <v>104</v>
       </c>
       <c r="I92" s="3" t="s">
@@ -7991,7 +7700,7 @@
       <c r="G93">
         <v>22197001</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="6" t="s">
         <v>105</v>
       </c>
       <c r="I93" s="3" t="s">
@@ -8026,7 +7735,7 @@
       <c r="G94">
         <v>22197003</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="6" t="s">
         <v>106</v>
       </c>
       <c r="I94" s="3" t="s">
@@ -8061,7 +7770,7 @@
       <c r="G95">
         <v>22197004</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="6" t="s">
         <v>107</v>
       </c>
       <c r="I95" s="3" t="s">
@@ -8096,7 +7805,7 @@
       <c r="G96">
         <v>22197005</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="6" t="s">
         <v>108</v>
       </c>
       <c r="I96" s="3" t="s">
@@ -8131,7 +7840,7 @@
       <c r="G97">
         <v>22197007</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="6" t="s">
         <v>109</v>
       </c>
       <c r="I97" s="3" t="s">
@@ -8166,7 +7875,7 @@
       <c r="G98">
         <v>22197008</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="6" t="s">
         <v>110</v>
       </c>
       <c r="I98" s="3" t="s">
@@ -8201,7 +7910,7 @@
       <c r="G99">
         <v>22197009</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="6">
         <v>2012</v>
       </c>
       <c r="I99" s="3" t="s">
@@ -8236,7 +7945,7 @@
       <c r="G100">
         <v>22197010</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I100" s="3" t="s">
@@ -8271,7 +7980,7 @@
       <c r="G101">
         <v>22197011</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="6" t="s">
         <v>112</v>
       </c>
       <c r="I101" s="3" t="s">
@@ -8306,7 +8015,7 @@
       <c r="G102">
         <v>22197012</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="6" t="s">
         <v>113</v>
       </c>
       <c r="I102" s="3" t="s">
@@ -8341,7 +8050,7 @@
       <c r="G103">
         <v>22197014</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="6" t="s">
         <v>114</v>
       </c>
       <c r="I103" s="3" t="s">
@@ -8376,7 +8085,7 @@
       <c r="G104">
         <v>2008204010</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="6" t="s">
         <v>115</v>
       </c>
       <c r="I104" s="3" t="s">
@@ -8411,7 +8120,7 @@
       <c r="G105">
         <v>385542</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="6">
         <v>2012</v>
       </c>
       <c r="I105" s="3" t="s">
@@ -8446,7 +8155,7 @@
       <c r="G106">
         <v>385544</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="6" t="s">
         <v>110</v>
       </c>
       <c r="I106" s="3" t="s">
@@ -8481,7 +8190,7 @@
       <c r="G107">
         <v>385547</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="6" t="s">
         <v>106</v>
       </c>
       <c r="I107" s="3" t="s">
@@ -8516,7 +8225,7 @@
       <c r="G108">
         <v>385550</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="6" t="s">
         <v>108</v>
       </c>
       <c r="I108" s="3" t="s">
@@ -8551,7 +8260,7 @@
       <c r="G109">
         <v>385552</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H109" s="6" t="s">
         <v>109</v>
       </c>
       <c r="I109" s="3" t="s">
@@ -8586,7 +8295,7 @@
       <c r="G110">
         <v>385554</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" s="6" t="s">
         <v>104</v>
       </c>
       <c r="I110" s="3" t="s">
@@ -8621,7 +8330,7 @@
       <c r="G111">
         <v>385556</v>
       </c>
-      <c r="H111" t="s">
+      <c r="H111" s="6" t="s">
         <v>105</v>
       </c>
       <c r="I111" s="3" t="s">
@@ -8656,7 +8365,7 @@
       <c r="G112">
         <v>385558</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H112" s="6" t="s">
         <v>107</v>
       </c>
       <c r="I112" s="3" t="s">
@@ -8691,7 +8400,7 @@
       <c r="G113">
         <v>385561</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H113" s="6" t="s">
         <v>118</v>
       </c>
       <c r="I113" s="3" t="s">
@@ -8726,7 +8435,7 @@
       <c r="G114">
         <v>385563</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H114" s="6" t="s">
         <v>119</v>
       </c>
       <c r="I114" s="3" t="s">
@@ -8761,7 +8470,7 @@
       <c r="G115">
         <v>385565</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H115" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I115" s="3" t="s">
@@ -8796,7 +8505,7 @@
       <c r="G116">
         <v>385566</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H116" s="6" t="s">
         <v>112</v>
       </c>
       <c r="I116" s="3" t="s">
@@ -8831,7 +8540,7 @@
       <c r="G117">
         <v>385568</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" s="6" t="s">
         <v>103</v>
       </c>
       <c r="I117" s="3" t="s">
@@ -8866,7 +8575,7 @@
       <c r="G118">
         <v>385576</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H118" s="6" t="s">
         <v>115</v>
       </c>
       <c r="I118" s="3" t="s">
@@ -8901,7 +8610,7 @@
       <c r="G119">
         <v>417953659</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H119" s="6" t="s">
         <v>120</v>
       </c>
       <c r="I119" s="3" t="s">
@@ -8936,7 +8645,7 @@
       <c r="G120">
         <v>422094252</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" s="6" t="s">
         <v>121</v>
       </c>
       <c r="I120" s="3" t="s">
@@ -8971,7 +8680,7 @@
       <c r="G121">
         <v>422094253</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H121" s="6" t="s">
         <v>122</v>
       </c>
       <c r="I121" s="3" t="s">
@@ -9006,7 +8715,7 @@
       <c r="G122">
         <v>422094254</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H122" s="6" t="s">
         <v>123</v>
       </c>
       <c r="I122" s="3" t="s">
@@ -9041,7 +8750,7 @@
       <c r="G123">
         <v>422104164</v>
       </c>
-      <c r="H123" t="s">
+      <c r="H123" s="6" t="s">
         <v>124</v>
       </c>
       <c r="I123" s="3" t="s">
@@ -9076,7 +8785,7 @@
       <c r="G124">
         <v>422104138</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H124" s="6" t="s">
         <v>125</v>
       </c>
       <c r="I124" s="3" t="s">
@@ -9111,7 +8820,7 @@
       <c r="G125">
         <v>422104166</v>
       </c>
-      <c r="H125" t="s">
+      <c r="H125" s="6" t="s">
         <v>126</v>
       </c>
       <c r="I125" s="3" t="s">
@@ -9146,7 +8855,7 @@
       <c r="G126">
         <v>417953658</v>
       </c>
-      <c r="H126" t="s">
+      <c r="H126" s="6" t="s">
         <v>127</v>
       </c>
       <c r="I126" s="3" t="s">
@@ -9181,7 +8890,7 @@
       <c r="G127">
         <v>422104165</v>
       </c>
-      <c r="H127" t="s">
+      <c r="H127" s="6" t="s">
         <v>128</v>
       </c>
       <c r="I127" s="3" t="s">
@@ -9216,7 +8925,7 @@
       <c r="G128">
         <v>422094255</v>
       </c>
-      <c r="H128" t="s">
+      <c r="H128" s="6" t="s">
         <v>129</v>
       </c>
       <c r="I128" s="3" t="s">
@@ -9251,7 +8960,7 @@
       <c r="G129">
         <v>422104167</v>
       </c>
-      <c r="H129" t="s">
+      <c r="H129" s="6" t="s">
         <v>130</v>
       </c>
       <c r="I129" s="3" t="s">
@@ -9286,7 +8995,7 @@
       <c r="G130">
         <v>422094256</v>
       </c>
-      <c r="H130" t="s">
+      <c r="H130" s="6" t="s">
         <v>131</v>
       </c>
       <c r="I130" s="3" t="s">
@@ -9321,7 +9030,7 @@
       <c r="G131">
         <v>422094257</v>
       </c>
-      <c r="H131" t="s">
+      <c r="H131" s="6" t="s">
         <v>132</v>
       </c>
       <c r="I131" s="3" t="s">
@@ -9356,7 +9065,7 @@
       <c r="G132">
         <v>385965</v>
       </c>
-      <c r="H132" t="s">
+      <c r="H132" s="6" t="s">
         <v>135</v>
       </c>
       <c r="I132" s="3" t="s">
@@ -9391,7 +9100,7 @@
       <c r="G133">
         <v>385967</v>
       </c>
-      <c r="H133" t="s">
+      <c r="H133" s="6" t="s">
         <v>136</v>
       </c>
       <c r="I133" s="3" t="s">
@@ -9426,7 +9135,7 @@
       <c r="G134">
         <v>385970</v>
       </c>
-      <c r="H134" t="s">
+      <c r="H134" s="6" t="s">
         <v>137</v>
       </c>
       <c r="I134" s="3" t="s">
@@ -9461,7 +9170,7 @@
       <c r="G135">
         <v>385973</v>
       </c>
-      <c r="H135" t="s">
+      <c r="H135" s="6" t="s">
         <v>138</v>
       </c>
       <c r="I135" s="3" t="s">
@@ -9496,7 +9205,7 @@
       <c r="G136">
         <v>385976</v>
       </c>
-      <c r="H136" t="s">
+      <c r="H136" s="6" t="s">
         <v>74</v>
       </c>
       <c r="I136" s="3" t="s">
@@ -9531,7 +9240,7 @@
       <c r="G137">
         <v>386021</v>
       </c>
-      <c r="H137" t="s">
+      <c r="H137" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I137" s="3" t="s">
@@ -9566,7 +9275,7 @@
       <c r="G138">
         <v>385979</v>
       </c>
-      <c r="H138" t="s">
+      <c r="H138" s="6" t="s">
         <v>9</v>
       </c>
       <c r="I138" s="3" t="s">
@@ -9601,7 +9310,7 @@
       <c r="G139">
         <v>385981</v>
       </c>
-      <c r="H139" t="s">
+      <c r="H139" s="6" t="s">
         <v>21</v>
       </c>
       <c r="I139" s="3" t="s">
@@ -9636,7 +9345,7 @@
       <c r="G140">
         <v>385984</v>
       </c>
-      <c r="H140" t="s">
+      <c r="H140" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I140" s="3" t="s">
@@ -9671,7 +9380,7 @@
       <c r="G141">
         <v>385987</v>
       </c>
-      <c r="H141" t="s">
+      <c r="H141" s="6" t="s">
         <v>61</v>
       </c>
       <c r="I141" s="3" t="s">
@@ -9706,7 +9415,7 @@
       <c r="G142">
         <v>385990</v>
       </c>
-      <c r="H142" t="s">
+      <c r="H142" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I142" s="3" t="s">
@@ -9741,7 +9450,7 @@
       <c r="G143">
         <v>386032</v>
       </c>
-      <c r="H143" t="s">
+      <c r="H143" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I143" s="3" t="s">
@@ -9776,7 +9485,7 @@
       <c r="G144">
         <v>385993</v>
       </c>
-      <c r="H144" t="s">
+      <c r="H144" s="6" t="s">
         <v>8</v>
       </c>
       <c r="I144" s="3" t="s">
@@ -9811,7 +9520,7 @@
       <c r="G145">
         <v>386034</v>
       </c>
-      <c r="H145" t="s">
+      <c r="H145" s="6" t="s">
         <v>18</v>
       </c>
       <c r="I145" s="3" t="s">
@@ -9846,7 +9555,7 @@
       <c r="G146">
         <v>385996</v>
       </c>
-      <c r="H146" t="s">
+      <c r="H146" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I146" s="3" t="s">
@@ -9881,7 +9590,7 @@
       <c r="G147">
         <v>385999</v>
       </c>
-      <c r="H147" t="s">
+      <c r="H147" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I147" s="3" t="s">
@@ -9916,7 +9625,7 @@
       <c r="G148">
         <v>386001</v>
       </c>
-      <c r="H148" t="s">
+      <c r="H148" s="6" t="s">
         <v>75</v>
       </c>
       <c r="I148" s="3" t="s">
@@ -9951,7 +9660,7 @@
       <c r="G149">
         <v>386005</v>
       </c>
-      <c r="H149" t="s">
+      <c r="H149" s="6" t="s">
         <v>62</v>
       </c>
       <c r="I149" s="3" t="s">
@@ -9986,7 +9695,7 @@
       <c r="G150">
         <v>386007</v>
       </c>
-      <c r="H150" t="s">
+      <c r="H150" s="6" t="s">
         <v>139</v>
       </c>
       <c r="I150" s="3" t="s">
@@ -10021,7 +9730,7 @@
       <c r="G151">
         <v>386010</v>
       </c>
-      <c r="H151" t="s">
+      <c r="H151" s="6" t="s">
         <v>140</v>
       </c>
       <c r="I151" s="3" t="s">
@@ -10056,7 +9765,7 @@
       <c r="G152">
         <v>386011</v>
       </c>
-      <c r="H152" t="s">
+      <c r="H152" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="3" t="s">
@@ -10091,7 +9800,7 @@
       <c r="G153">
         <v>386014</v>
       </c>
-      <c r="H153" t="s">
+      <c r="H153" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I153" s="3" t="s">
@@ -10126,7 +9835,7 @@
       <c r="G154">
         <v>386017</v>
       </c>
-      <c r="H154" t="s">
+      <c r="H154" s="6" t="s">
         <v>34</v>
       </c>
       <c r="I154" s="3" t="s">
@@ -10161,7 +9870,7 @@
       <c r="G155">
         <v>386025</v>
       </c>
-      <c r="H155" t="s">
+      <c r="H155" s="6" t="s">
         <v>141</v>
       </c>
       <c r="I155" s="3" t="s">
@@ -10196,7 +9905,7 @@
       <c r="G156">
         <v>386028</v>
       </c>
-      <c r="H156" t="s">
+      <c r="H156" s="6" t="s">
         <v>142</v>
       </c>
       <c r="I156" s="3" t="s">
@@ -10206,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -10231,7 +9940,7 @@
       <c r="G157">
         <v>386030</v>
       </c>
-      <c r="H157" t="s">
+      <c r="H157" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I157" s="3" t="s">
@@ -10266,7 +9975,7 @@
       <c r="G158">
         <v>386035</v>
       </c>
-      <c r="H158" t="s">
+      <c r="H158" s="6" t="s">
         <v>38</v>
       </c>
       <c r="I158" s="3" t="s">
@@ -10301,7 +10010,7 @@
       <c r="G159">
         <v>386036</v>
       </c>
-      <c r="H159" t="s">
+      <c r="H159" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I159" s="3" t="s">
@@ -10336,7 +10045,7 @@
       <c r="G160">
         <v>386038</v>
       </c>
-      <c r="H160" t="s">
+      <c r="H160" s="6" t="s">
         <v>143</v>
       </c>
       <c r="I160" s="3" t="s">
@@ -10371,7 +10080,7 @@
       <c r="G161">
         <v>386040</v>
       </c>
-      <c r="H161" t="s">
+      <c r="H161" s="6" t="s">
         <v>144</v>
       </c>
       <c r="I161" s="3" t="s">
@@ -10392,7 +10101,7 @@
         <v>2740205</v>
       </c>
       <c r="C162" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D162" t="s">
         <v>153</v>
@@ -10406,11 +10115,11 @@
       <c r="G162">
         <v>28181103</v>
       </c>
-      <c r="H162" t="s">
+      <c r="H162" s="6" t="s">
         <v>154</v>
       </c>
       <c r="I162" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -10427,7 +10136,7 @@
         <v>2740205</v>
       </c>
       <c r="C163" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D163" t="s">
         <v>153</v>
@@ -10441,17 +10150,17 @@
       <c r="G163">
         <v>28181105</v>
       </c>
-      <c r="H163" t="s">
-        <v>155</v>
+      <c r="H163" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="I163" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J163">
         <v>1</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -10462,7 +10171,7 @@
         <v>2740205</v>
       </c>
       <c r="C164" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D164" t="s">
         <v>153</v>
@@ -10476,11 +10185,11 @@
       <c r="G164">
         <v>28181107</v>
       </c>
-      <c r="H164" t="s">
-        <v>156</v>
+      <c r="H164" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="I164" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J164">
         <v>1</v>
@@ -10497,7 +10206,7 @@
         <v>2740205</v>
       </c>
       <c r="C165" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D165" t="s">
         <v>153</v>
@@ -10511,11 +10220,11 @@
       <c r="G165">
         <v>28181109</v>
       </c>
-      <c r="H165" t="s">
-        <v>157</v>
+      <c r="H165" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="I165" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J165">
         <v>1</v>
@@ -10532,7 +10241,7 @@
         <v>2740205</v>
       </c>
       <c r="C166" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D166" t="s">
         <v>153</v>
@@ -10546,11 +10255,11 @@
       <c r="G166">
         <v>28181111</v>
       </c>
-      <c r="H166" t="s">
+      <c r="H166" s="6" t="s">
         <v>109</v>
       </c>
       <c r="I166" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -10567,7 +10276,7 @@
         <v>2740205</v>
       </c>
       <c r="C167" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D167" t="s">
         <v>153</v>
@@ -10581,11 +10290,11 @@
       <c r="G167">
         <v>28181113</v>
       </c>
-      <c r="H167" t="s">
-        <v>158</v>
+      <c r="H167" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="I167" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J167">
         <v>1</v>
@@ -10602,7 +10311,7 @@
         <v>2740205</v>
       </c>
       <c r="C168" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D168" t="s">
         <v>153</v>
@@ -10616,11 +10325,11 @@
       <c r="G168">
         <v>28181115</v>
       </c>
-      <c r="H168" t="s">
+      <c r="H168" s="6" t="s">
         <v>62</v>
       </c>
       <c r="I168" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J168">
         <v>1</v>
@@ -10637,7 +10346,7 @@
         <v>2740205</v>
       </c>
       <c r="C169" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D169" t="s">
         <v>153</v>
@@ -10651,11 +10360,11 @@
       <c r="G169">
         <v>28181117</v>
       </c>
-      <c r="H169" t="s">
+      <c r="H169" s="6" t="s">
         <v>90</v>
       </c>
       <c r="I169" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J169">
         <v>1</v>
@@ -10672,7 +10381,7 @@
         <v>2740205</v>
       </c>
       <c r="C170" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D170" t="s">
         <v>153</v>
@@ -10686,11 +10395,11 @@
       <c r="G170">
         <v>28181119</v>
       </c>
-      <c r="H170" t="s">
+      <c r="H170" s="6" t="s">
         <v>138</v>
       </c>
       <c r="I170" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J170">
         <v>1</v>
@@ -10707,7 +10416,7 @@
         <v>2740205</v>
       </c>
       <c r="C171" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D171" t="s">
         <v>153</v>
@@ -10721,11 +10430,11 @@
       <c r="G171">
         <v>28181121</v>
       </c>
-      <c r="H171" t="s">
-        <v>159</v>
+      <c r="H171" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="I171" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J171">
         <v>1</v>
@@ -10742,7 +10451,7 @@
         <v>2740205</v>
       </c>
       <c r="C172" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D172" t="s">
         <v>153</v>
@@ -10756,11 +10465,11 @@
       <c r="G172">
         <v>28181123</v>
       </c>
-      <c r="H172" t="s">
+      <c r="H172" s="6" t="s">
         <v>105</v>
       </c>
       <c r="I172" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J172">
         <v>1</v>
@@ -10777,7 +10486,7 @@
         <v>2740205</v>
       </c>
       <c r="C173" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D173" t="s">
         <v>153</v>
@@ -10791,11 +10500,11 @@
       <c r="G173">
         <v>28181125</v>
       </c>
-      <c r="H173" t="s">
+      <c r="H173" s="6" t="s">
         <v>104</v>
       </c>
       <c r="I173" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J173">
         <v>1</v>
@@ -10812,7 +10521,7 @@
         <v>2740205</v>
       </c>
       <c r="C174" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D174" t="s">
         <v>153</v>
@@ -10826,11 +10535,11 @@
       <c r="G174">
         <v>28181127</v>
       </c>
-      <c r="H174" t="s">
+      <c r="H174" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I174" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J174">
         <v>1</v>
@@ -10847,7 +10556,7 @@
         <v>2740205</v>
       </c>
       <c r="C175" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D175" t="s">
         <v>153</v>
@@ -10861,17 +10570,17 @@
       <c r="G175">
         <v>28181129</v>
       </c>
-      <c r="H175" t="s">
-        <v>160</v>
+      <c r="H175" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="I175" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J175">
         <v>1</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -10882,7 +10591,7 @@
         <v>2740205</v>
       </c>
       <c r="C176" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D176" t="s">
         <v>153</v>
@@ -10896,17 +10605,17 @@
       <c r="G176">
         <v>28181131</v>
       </c>
-      <c r="H176" t="s">
+      <c r="H176" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I176" t="s">
         <v>161</v>
       </c>
-      <c r="I176" t="s">
-        <v>164</v>
-      </c>
       <c r="J176">
         <v>1</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -10917,7 +10626,7 @@
         <v>2740205</v>
       </c>
       <c r="C177" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D177" t="s">
         <v>153</v>
@@ -10931,11 +10640,11 @@
       <c r="G177">
         <v>28181104</v>
       </c>
-      <c r="H177" t="s">
-        <v>162</v>
+      <c r="H177" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="I177" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J177">
         <v>1</v>
@@ -10952,7 +10661,7 @@
         <v>2740205</v>
       </c>
       <c r="C178" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D178" t="s">
         <v>153</v>
@@ -10966,11 +10675,11 @@
       <c r="G178">
         <v>28181106</v>
       </c>
-      <c r="H178" t="s">
+      <c r="H178" s="6" t="s">
         <v>98</v>
       </c>
       <c r="I178" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J178">
         <v>1</v>
@@ -10987,7 +10696,7 @@
         <v>2740205</v>
       </c>
       <c r="C179" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D179" t="s">
         <v>153</v>
@@ -11001,11 +10710,11 @@
       <c r="G179">
         <v>28181108</v>
       </c>
-      <c r="H179" t="s">
+      <c r="H179" s="6" t="s">
         <v>99</v>
       </c>
       <c r="I179" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J179">
         <v>1</v>
@@ -11022,7 +10731,7 @@
         <v>2740205</v>
       </c>
       <c r="C180" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D180" t="s">
         <v>153</v>
@@ -11036,11 +10745,11 @@
       <c r="G180">
         <v>28181110</v>
       </c>
-      <c r="H180" t="s">
-        <v>163</v>
+      <c r="H180" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="I180" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J180">
         <v>1</v>
@@ -11057,7 +10766,7 @@
         <v>2740205</v>
       </c>
       <c r="C181" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D181" t="s">
         <v>153</v>
@@ -11071,11 +10780,11 @@
       <c r="G181">
         <v>28181112</v>
       </c>
-      <c r="H181" t="s">
+      <c r="H181" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I181" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J181">
         <v>1</v>
@@ -11092,7 +10801,7 @@
         <v>2740205</v>
       </c>
       <c r="C182" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D182" t="s">
         <v>153</v>
@@ -11106,11 +10815,11 @@
       <c r="G182">
         <v>28181114</v>
       </c>
-      <c r="H182" t="s">
+      <c r="H182" s="6" t="s">
         <v>107</v>
       </c>
       <c r="I182" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J182">
         <v>1</v>
@@ -11127,7 +10836,7 @@
         <v>2740205</v>
       </c>
       <c r="C183" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D183" t="s">
         <v>153</v>
@@ -11141,11 +10850,11 @@
       <c r="G183">
         <v>28181116</v>
       </c>
-      <c r="H183" t="s">
+      <c r="H183" s="6" t="s">
         <v>61</v>
       </c>
       <c r="I183" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J183">
         <v>1</v>
@@ -11162,7 +10871,7 @@
         <v>2740205</v>
       </c>
       <c r="C184" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D184" t="s">
         <v>153</v>
@@ -11176,11 +10885,11 @@
       <c r="G184">
         <v>28181118</v>
       </c>
-      <c r="H184" t="s">
+      <c r="H184" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I184" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J184">
         <v>1</v>
@@ -11197,7 +10906,7 @@
         <v>2740205</v>
       </c>
       <c r="C185" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D185" t="s">
         <v>153</v>
@@ -11211,11 +10920,11 @@
       <c r="G185">
         <v>28181120</v>
       </c>
-      <c r="H185" t="s">
+      <c r="H185" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I185" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J185">
         <v>1</v>
@@ -11232,7 +10941,7 @@
         <v>2740205</v>
       </c>
       <c r="C186" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D186" t="s">
         <v>153</v>
@@ -11246,11 +10955,11 @@
       <c r="G186">
         <v>28181122</v>
       </c>
-      <c r="H186" t="s">
+      <c r="H186" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I186" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J186">
         <v>1</v>
@@ -11267,7 +10976,7 @@
         <v>2740205</v>
       </c>
       <c r="C187" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D187" t="s">
         <v>153</v>
@@ -11281,11 +10990,11 @@
       <c r="G187">
         <v>28181124</v>
       </c>
-      <c r="H187" t="s">
+      <c r="H187" s="6" t="s">
         <v>47</v>
       </c>
       <c r="I187" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J187">
         <v>1</v>
@@ -11302,7 +11011,7 @@
         <v>2740205</v>
       </c>
       <c r="C188" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D188" t="s">
         <v>153</v>
@@ -11316,11 +11025,11 @@
       <c r="G188">
         <v>28181126</v>
       </c>
-      <c r="H188" t="s">
+      <c r="H188" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I188" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J188">
         <v>1</v>
@@ -11337,7 +11046,7 @@
         <v>2740205</v>
       </c>
       <c r="C189" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D189" t="s">
         <v>153</v>
@@ -11351,11 +11060,11 @@
       <c r="G189">
         <v>28181128</v>
       </c>
-      <c r="H189" t="s">
+      <c r="H189" s="6" t="s">
         <v>112</v>
       </c>
       <c r="I189" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J189">
         <v>1</v>
@@ -11372,7 +11081,7 @@
         <v>2740205</v>
       </c>
       <c r="C190" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D190" t="s">
         <v>153</v>
@@ -11386,11 +11095,11 @@
       <c r="G190">
         <v>28181130</v>
       </c>
-      <c r="H190" t="s">
+      <c r="H190" s="6" t="s">
         <v>96</v>
       </c>
       <c r="I190" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J190">
         <v>1</v>
@@ -11407,7 +11116,7 @@
         <v>2740205</v>
       </c>
       <c r="C191" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D191" t="s">
         <v>153</v>
@@ -11421,11 +11130,11 @@
       <c r="G191">
         <v>28181132</v>
       </c>
-      <c r="H191" t="s">
+      <c r="H191" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I191" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J191">
         <v>1</v>
@@ -11443,12 +11152,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7089906A-4084-CE42-A748-343F53CDD52F}">
-  <dimension ref="A3:C206"/>
+  <dimension ref="A3:B141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="39.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="18.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
@@ -11557,1674 +11265,1115 @@
     <col min="132" max="132" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>162</v>
+      </c>
+      <c r="B3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" t="s">
+      <c r="B7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>2012</v>
+      </c>
+      <c r="B32" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>158</v>
+      </c>
+      <c r="B65" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>50</v>
+      </c>
+      <c r="B68" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>55</v>
+      </c>
+      <c r="B74" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>93</v>
+      </c>
+      <c r="B80" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>122</v>
+      </c>
+      <c r="B82" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>33</v>
+      </c>
+      <c r="B85" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>66</v>
+      </c>
+      <c r="B86" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>159</v>
+      </c>
+      <c r="B89" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>85</v>
+      </c>
+      <c r="B91" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>10</v>
+      </c>
+      <c r="B92" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B94" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>127</v>
+      </c>
+      <c r="B95" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>69</v>
+      </c>
+      <c r="B96" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>128</v>
+      </c>
+      <c r="B97" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>84</v>
+      </c>
+      <c r="B98" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>95</v>
+      </c>
+      <c r="B99" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>20</v>
+      </c>
+      <c r="B100" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>65</v>
+      </c>
+      <c r="B101" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="B13" t="s">
+      <c r="B102" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>97</v>
+      </c>
+      <c r="B103" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>19</v>
+      </c>
+      <c r="B104" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>48</v>
+      </c>
+      <c r="B106" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>131</v>
+      </c>
+      <c r="B107" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>53</v>
+      </c>
+      <c r="B108" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>120</v>
+      </c>
+      <c r="B109" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>144</v>
+      </c>
+      <c r="B110" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>41</v>
+      </c>
+      <c r="B111" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>80</v>
+      </c>
+      <c r="B112" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>157</v>
+      </c>
+      <c r="B113" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>59</v>
+      </c>
+      <c r="B114" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>141</v>
+      </c>
+      <c r="B115" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>155</v>
+      </c>
+      <c r="B117" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>129</v>
+      </c>
+      <c r="B119" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>156</v>
+      </c>
+      <c r="B120" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>71</v>
+      </c>
+      <c r="B121" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>17</v>
+      </c>
+      <c r="B122" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>91</v>
+      </c>
+      <c r="B123" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>13</v>
+      </c>
+      <c r="B124" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="B14" t="s">
+      <c r="B126" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>68</v>
+      </c>
+      <c r="B127" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C16" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="B18" t="s">
+      <c r="B128" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>72</v>
+      </c>
+      <c r="B129" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>56</v>
+      </c>
+      <c r="B130" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>160</v>
+      </c>
+      <c r="B131" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>42</v>
+      </c>
+      <c r="B132" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>54</v>
+      </c>
+      <c r="B133" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
         <v>154</v>
       </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="B20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="B23" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="B24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="B26" t="s">
-        <v>162</v>
-      </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="B27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="B29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="B30" t="s">
-        <v>158</v>
-      </c>
-      <c r="C30" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="B31" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="B32" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="B33" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="B34" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="B35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="B36" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="B37" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="B38" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="B39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="B40" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="B41" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="B42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="B43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="B44" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="B45" t="s">
-        <v>160</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="B46" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>168</v>
-      </c>
-      <c r="C47" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>116</v>
-      </c>
-      <c r="B48">
-        <v>2012</v>
-      </c>
-      <c r="C48" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="B49" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="B50" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="B51" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="B52" t="s">
-        <v>111</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="B54" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="B55" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="B56" t="s">
-        <v>107</v>
-      </c>
-      <c r="C56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="B57" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="B58" t="s">
-        <v>104</v>
-      </c>
-      <c r="C58" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="B59" t="s">
-        <v>106</v>
-      </c>
-      <c r="C59" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="B60" t="s">
-        <v>105</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="B61" t="s">
-        <v>103</v>
-      </c>
-      <c r="C61" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>169</v>
-      </c>
-      <c r="C62" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>117</v>
-      </c>
-      <c r="B63">
-        <v>2012</v>
-      </c>
-      <c r="C63" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="B64" t="s">
-        <v>119</v>
-      </c>
-      <c r="C64" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="B65" t="s">
-        <v>115</v>
-      </c>
-      <c r="C65" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="B66" t="s">
-        <v>110</v>
-      </c>
-      <c r="C66" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="B67" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="B68" t="s">
-        <v>109</v>
-      </c>
-      <c r="C68" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="B69" t="s">
-        <v>118</v>
-      </c>
-      <c r="C69" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="B70" t="s">
-        <v>112</v>
-      </c>
-      <c r="C70" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="B71" t="s">
-        <v>107</v>
-      </c>
-      <c r="C71" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="B72" t="s">
-        <v>108</v>
-      </c>
-      <c r="C72" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="B73" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="B74" t="s">
-        <v>106</v>
-      </c>
-      <c r="C74" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="B75" t="s">
-        <v>105</v>
-      </c>
-      <c r="C75" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="B76" t="s">
-        <v>103</v>
-      </c>
-      <c r="C76" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>170</v>
-      </c>
-      <c r="C77" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="B80" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="B81" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="B82" t="s">
-        <v>8</v>
-      </c>
-      <c r="C82" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="B83" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="B84" t="s">
-        <v>13</v>
-      </c>
-      <c r="C84" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="B85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="B86" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="B87" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="B88" t="s">
-        <v>14</v>
-      </c>
-      <c r="C88" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="B89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C89" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" t="s">
-        <v>171</v>
-      </c>
-      <c r="C90" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
-        <v>100</v>
-      </c>
-      <c r="B91" t="s">
-        <v>93</v>
-      </c>
-      <c r="C91" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="B92" t="s">
-        <v>95</v>
-      </c>
-      <c r="C92" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="B93" t="s">
-        <v>97</v>
-      </c>
-      <c r="C93" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="B94" t="s">
-        <v>100</v>
-      </c>
-      <c r="C94" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="B95" t="s">
-        <v>92</v>
-      </c>
-      <c r="C95" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="B96" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="B97" t="s">
-        <v>99</v>
-      </c>
-      <c r="C97" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="B98" t="s">
-        <v>91</v>
-      </c>
-      <c r="C98" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="B99" t="s">
-        <v>90</v>
-      </c>
-      <c r="C99" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="B100" t="s">
-        <v>96</v>
-      </c>
-      <c r="C100" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="B101" t="s">
-        <v>101</v>
-      </c>
-      <c r="C101" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="B102" t="s">
-        <v>98</v>
-      </c>
-      <c r="C102" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" t="s">
-        <v>172</v>
-      </c>
-      <c r="C103" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" t="s">
-        <v>43</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="B134" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
         <v>36</v>
       </c>
-      <c r="C104" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="B105" t="s">
-        <v>39</v>
-      </c>
-      <c r="C105" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="B106" t="s">
-        <v>41</v>
-      </c>
-      <c r="C106" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="B107" t="s">
-        <v>34</v>
-      </c>
-      <c r="C107" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="B108" t="s">
-        <v>42</v>
-      </c>
-      <c r="C108" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="B109" t="s">
-        <v>37</v>
-      </c>
-      <c r="C109" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="B110" t="s">
-        <v>40</v>
-      </c>
-      <c r="C110" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="B111" t="s">
-        <v>33</v>
-      </c>
-      <c r="C111" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="B112" t="s">
-        <v>43</v>
-      </c>
-      <c r="C112" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="B113" t="s">
-        <v>35</v>
-      </c>
-      <c r="C113" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="B114" t="s">
-        <v>32</v>
-      </c>
-      <c r="C114" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="B115" t="s">
-        <v>38</v>
-      </c>
-      <c r="C115" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>173</v>
-      </c>
-      <c r="C116" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" t="s">
-        <v>71</v>
-      </c>
-      <c r="B117" t="s">
-        <v>70</v>
-      </c>
-      <c r="C117" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="B118" t="s">
-        <v>68</v>
-      </c>
-      <c r="C118" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="B119" t="s">
-        <v>67</v>
-      </c>
-      <c r="C119" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="B120" t="s">
-        <v>62</v>
-      </c>
-      <c r="C120" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="B121" t="s">
-        <v>63</v>
-      </c>
-      <c r="C121" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="B122" t="s">
-        <v>73</v>
-      </c>
-      <c r="C122" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="B123" t="s">
-        <v>65</v>
-      </c>
-      <c r="C123" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="B124" t="s">
-        <v>71</v>
-      </c>
-      <c r="C124" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="B125" t="s">
-        <v>72</v>
-      </c>
-      <c r="C125" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="B126" t="s">
-        <v>61</v>
-      </c>
-      <c r="C126" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="B127" t="s">
-        <v>69</v>
-      </c>
-      <c r="C127" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="B128" t="s">
-        <v>64</v>
-      </c>
-      <c r="C128" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="B129" t="s">
-        <v>66</v>
-      </c>
-      <c r="C129" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" t="s">
-        <v>174</v>
-      </c>
-      <c r="C130" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" t="s">
-        <v>54</v>
-      </c>
-      <c r="B131" t="s">
-        <v>48</v>
-      </c>
-      <c r="C131" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="B132" t="s">
-        <v>51</v>
-      </c>
-      <c r="C132" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="B133" t="s">
-        <v>47</v>
-      </c>
-      <c r="C133" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="B134" t="s">
-        <v>50</v>
-      </c>
-      <c r="C134" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="B135" t="s">
-        <v>49</v>
-      </c>
-      <c r="C135" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="B136" t="s">
-        <v>46</v>
-      </c>
-      <c r="C136" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="B137" t="s">
-        <v>52</v>
-      </c>
-      <c r="C137" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="B138" t="s">
+      <c r="B135" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>132</v>
+      </c>
+      <c r="B136" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>88</v>
+      </c>
+      <c r="B137" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>78</v>
+      </c>
+      <c r="B138" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>76</v>
+      </c>
+      <c r="B139" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
         <v>45</v>
       </c>
-      <c r="C138" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="B139" t="s">
-        <v>57</v>
-      </c>
-      <c r="C139" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="B140" t="s">
-        <v>54</v>
-      </c>
-      <c r="C140" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="B141" t="s">
-        <v>58</v>
-      </c>
-      <c r="C141" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="B142" t="s">
-        <v>55</v>
-      </c>
-      <c r="C142" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="B143" t="s">
-        <v>53</v>
-      </c>
-      <c r="C143" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="B144" t="s">
-        <v>59</v>
-      </c>
-      <c r="C144" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="B145" t="s">
-        <v>56</v>
-      </c>
-      <c r="C145" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" t="s">
-        <v>175</v>
-      </c>
-      <c r="C146" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" t="s">
-        <v>77</v>
-      </c>
-      <c r="B147" t="s">
-        <v>85</v>
-      </c>
-      <c r="C147" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="B148" t="s">
-        <v>83</v>
-      </c>
-      <c r="C148" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="B149" t="s">
-        <v>86</v>
-      </c>
-      <c r="C149" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="B150" t="s">
-        <v>81</v>
-      </c>
-      <c r="C150" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="B151" t="s">
-        <v>76</v>
-      </c>
-      <c r="C151" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="B152" t="s">
-        <v>88</v>
-      </c>
-      <c r="C152" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="B153" t="s">
-        <v>78</v>
-      </c>
-      <c r="C153" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="B154" t="s">
-        <v>84</v>
-      </c>
-      <c r="C154" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="B155" t="s">
-        <v>77</v>
-      </c>
-      <c r="C155" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="B156" t="s">
-        <v>79</v>
-      </c>
-      <c r="C156" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="B157" t="s">
-        <v>80</v>
-      </c>
-      <c r="C157" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="B158" t="s">
-        <v>87</v>
-      </c>
-      <c r="C158" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="B159" t="s">
-        <v>82</v>
-      </c>
-      <c r="C159" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
-        <v>176</v>
-      </c>
-      <c r="C160" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" t="s">
-        <v>145</v>
-      </c>
-      <c r="B161" t="s">
-        <v>18</v>
-      </c>
-      <c r="C161" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="B162" t="s">
-        <v>141</v>
-      </c>
-      <c r="C162" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="B163" t="s">
-        <v>30</v>
-      </c>
-      <c r="C163" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="B164" t="s">
-        <v>49</v>
-      </c>
-      <c r="C164" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="B165" t="s">
-        <v>8</v>
-      </c>
-      <c r="C165" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="B166" t="s">
-        <v>25</v>
-      </c>
-      <c r="C166" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="B167" t="s">
-        <v>34</v>
-      </c>
-      <c r="C167" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="B168" t="s">
-        <v>46</v>
-      </c>
-      <c r="C168" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="B169" t="s">
-        <v>26</v>
-      </c>
-      <c r="C169" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="B170" t="s">
-        <v>37</v>
-      </c>
-      <c r="C170" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="B171" t="s">
-        <v>139</v>
-      </c>
-      <c r="C171" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="B172" t="s">
-        <v>62</v>
-      </c>
-      <c r="C172" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="B173" t="s">
-        <v>142</v>
-      </c>
-      <c r="C173" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="B174" t="s">
-        <v>138</v>
-      </c>
-      <c r="C174" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="B175" t="s">
-        <v>137</v>
-      </c>
-      <c r="C175" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="B176" t="s">
-        <v>140</v>
-      </c>
-      <c r="C176" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="B177" t="s">
-        <v>43</v>
-      </c>
-      <c r="C177" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="B178" t="s">
-        <v>61</v>
-      </c>
-      <c r="C178" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="B179" t="s">
-        <v>74</v>
-      </c>
-      <c r="C179" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="B180" t="s">
-        <v>143</v>
-      </c>
-      <c r="C180" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="B181" t="s">
-        <v>75</v>
-      </c>
-      <c r="C181" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="B182" t="s">
-        <v>144</v>
-      </c>
-      <c r="C182" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="B183" t="s">
-        <v>23</v>
-      </c>
-      <c r="C183" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="B184" t="s">
-        <v>136</v>
-      </c>
-      <c r="C184" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="B185" t="s">
-        <v>9</v>
-      </c>
-      <c r="C185" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="B186" t="s">
-        <v>38</v>
-      </c>
-      <c r="C186" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="B187" t="s">
-        <v>14</v>
-      </c>
-      <c r="C187" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="B188" t="s">
-        <v>135</v>
-      </c>
-      <c r="C188" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="B189" t="s">
-        <v>15</v>
-      </c>
-      <c r="C189" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="B190" t="s">
-        <v>21</v>
-      </c>
-      <c r="C190" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" t="s">
-        <v>177</v>
-      </c>
-      <c r="C191" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" t="s">
-        <v>133</v>
-      </c>
-      <c r="B192" t="s">
-        <v>121</v>
-      </c>
-      <c r="C192" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="B193" t="s">
-        <v>122</v>
-      </c>
-      <c r="C193" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="B194" t="s">
-        <v>125</v>
-      </c>
-      <c r="C194" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="B195" t="s">
-        <v>127</v>
-      </c>
-      <c r="C195" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="B196" t="s">
-        <v>124</v>
-      </c>
-      <c r="C196" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="B197" t="s">
-        <v>131</v>
-      </c>
-      <c r="C197" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="B198" t="s">
-        <v>120</v>
-      </c>
-      <c r="C198" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="B199" t="s">
-        <v>129</v>
-      </c>
-      <c r="C199" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="B200" t="s">
-        <v>126</v>
-      </c>
-      <c r="C200" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="B201" t="s">
-        <v>123</v>
-      </c>
-      <c r="C201" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="B202" t="s">
-        <v>130</v>
-      </c>
-      <c r="C202" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="B203" t="s">
-        <v>132</v>
-      </c>
-      <c r="C203" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="B204" t="s">
-        <v>128</v>
-      </c>
-      <c r="C204" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" t="s">
-        <v>178</v>
-      </c>
-      <c r="C205" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" t="s">
+      <c r="B140" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
         <v>150</v>
       </c>
-      <c r="C206" s="5">
+      <c r="B141" s="5">
         <v>190</v>
       </c>
     </row>

--- a/songs/mayday/data/mayday_songs.xlsx
+++ b/songs/mayday/data/mayday_songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1/Code/net_charts/songs/mayday/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBAB643-C777-804B-A95E-7FCF19F2FEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B893A492-C382-F045-99AD-3CEDE9091DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15940" yWindow="600" windowWidth="28100" windowHeight="17360" xr2:uid="{83F95A99-0641-214A-BFE5-EC231FCA42BA}"/>
+    <workbookView xWindow="-3060" yWindow="1540" windowWidth="28100" windowHeight="17360" xr2:uid="{83F95A99-0641-214A-BFE5-EC231FCA42BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4447,6 +4447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DE93CF-E5FB-F14D-BF46-645C5C24B710}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K191"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -8098,7 +8099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" hidden="1">
       <c r="A105">
         <v>8</v>
       </c>
@@ -8133,7 +8134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" hidden="1">
       <c r="A106">
         <v>8</v>
       </c>
@@ -8168,7 +8169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" hidden="1">
       <c r="A107">
         <v>8</v>
       </c>
@@ -8203,7 +8204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" hidden="1">
       <c r="A108">
         <v>8</v>
       </c>
@@ -8238,7 +8239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" hidden="1">
       <c r="A109">
         <v>8</v>
       </c>
@@ -8273,7 +8274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" hidden="1">
       <c r="A110">
         <v>8</v>
       </c>
@@ -8308,7 +8309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" hidden="1">
       <c r="A111">
         <v>8</v>
       </c>
@@ -8343,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" hidden="1">
       <c r="A112">
         <v>8</v>
       </c>
@@ -8448,7 +8449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" hidden="1">
       <c r="A115">
         <v>8</v>
       </c>
@@ -8483,7 +8484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" hidden="1">
       <c r="A116">
         <v>8</v>
       </c>
@@ -8518,7 +8519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" hidden="1">
       <c r="A117">
         <v>8</v>
       </c>
@@ -8553,7 +8554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" hidden="1">
       <c r="A118">
         <v>8</v>
       </c>
@@ -9218,7 +9219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" hidden="1">
       <c r="A137">
         <v>10</v>
       </c>
@@ -9253,7 +9254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" hidden="1">
       <c r="A138">
         <v>10</v>
       </c>
@@ -9288,7 +9289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" hidden="1">
       <c r="A139">
         <v>10</v>
       </c>
@@ -9323,7 +9324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" hidden="1">
       <c r="A140">
         <v>10</v>
       </c>
@@ -9358,7 +9359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" hidden="1">
       <c r="A141">
         <v>10</v>
       </c>
@@ -9393,7 +9394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" hidden="1">
       <c r="A142">
         <v>10</v>
       </c>
@@ -9428,7 +9429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" hidden="1">
       <c r="A143">
         <v>10</v>
       </c>
@@ -9463,7 +9464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" hidden="1">
       <c r="A144">
         <v>10</v>
       </c>
@@ -9498,7 +9499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" hidden="1">
       <c r="A145">
         <v>10</v>
       </c>
@@ -9533,7 +9534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" hidden="1">
       <c r="A146">
         <v>10</v>
       </c>
@@ -9568,7 +9569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" hidden="1">
       <c r="A147">
         <v>10</v>
       </c>
@@ -9638,7 +9639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149">
         <v>10</v>
       </c>
@@ -9743,7 +9744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" hidden="1">
       <c r="A152">
         <v>10</v>
       </c>
@@ -9778,7 +9779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" hidden="1">
       <c r="A153">
         <v>10</v>
       </c>
@@ -9813,7 +9814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" hidden="1">
       <c r="A154">
         <v>10</v>
       </c>
@@ -9883,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" hidden="1">
       <c r="A156">
         <v>10</v>
       </c>
@@ -9918,7 +9919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" hidden="1">
       <c r="A157">
         <v>10</v>
       </c>
@@ -9953,7 +9954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" hidden="1">
       <c r="A158">
         <v>10</v>
       </c>
@@ -9988,7 +9989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" hidden="1">
       <c r="A159">
         <v>10</v>
       </c>
@@ -10128,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" hidden="1">
       <c r="A163">
         <v>11</v>
       </c>
@@ -10233,7 +10234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" hidden="1">
       <c r="A166">
         <v>11</v>
       </c>
@@ -10303,7 +10304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" hidden="1">
       <c r="A168">
         <v>11</v>
       </c>
@@ -10338,7 +10339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" hidden="1">
       <c r="A169">
         <v>11</v>
       </c>
@@ -10373,7 +10374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170">
         <v>11</v>
       </c>
@@ -10443,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" hidden="1">
       <c r="A172">
         <v>11</v>
       </c>
@@ -10478,7 +10479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" hidden="1">
       <c r="A173">
         <v>11</v>
       </c>
@@ -10513,7 +10514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" hidden="1">
       <c r="A174">
         <v>11</v>
       </c>
@@ -10548,7 +10549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" hidden="1">
       <c r="A175">
         <v>11</v>
       </c>
@@ -10583,7 +10584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176">
         <v>11</v>
       </c>
@@ -10653,7 +10654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" hidden="1">
       <c r="A178">
         <v>11</v>
       </c>
@@ -10688,7 +10689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" hidden="1">
       <c r="A179">
         <v>11</v>
       </c>
@@ -10758,7 +10759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181">
         <v>11</v>
       </c>
@@ -10793,7 +10794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182">
         <v>11</v>
       </c>
@@ -10828,7 +10829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" hidden="1">
       <c r="A183">
         <v>11</v>
       </c>
@@ -10863,7 +10864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" hidden="1">
       <c r="A184">
         <v>11</v>
       </c>
@@ -10898,7 +10899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" hidden="1">
       <c r="A185">
         <v>11</v>
       </c>
@@ -10933,7 +10934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" hidden="1">
       <c r="A186">
         <v>11</v>
       </c>
@@ -10968,7 +10969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187">
         <v>11</v>
       </c>
@@ -11003,7 +11004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188">
         <v>11</v>
       </c>
@@ -11038,7 +11039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189">
         <v>11</v>
       </c>
@@ -11073,7 +11074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190">
         <v>11</v>
       </c>
@@ -11108,7 +11109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191">
         <v>11</v>
       </c>
@@ -11144,6 +11145,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K191" xr:uid="{F8DE93CF-E5FB-F14D-BF46-645C5C24B710}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
